--- a/appium-tests/Appium_Test_Report.xlsx
+++ b/appium-tests/Appium_Test_Report.xlsx
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>6/8/2026, 3:54:36 pm</t>
+    <t>6/8/2026, 7:07:05 pm</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-06T10:24:36.608Z</t>
+    <t>2026-08-06T13:37:05.079Z</t>
   </si>
   <si>
     <t>TC-MOB-002</t>
@@ -185,7 +185,7 @@
     <t>Capacitor Android Native Bridge Call #2</t>
   </si>
   <si>
-    <t>2026-08-06T10:24:36.610Z</t>
+    <t>2026-08-06T13:37:05.080Z</t>
   </si>
   <si>
     <t>TC-MOB-003</t>
@@ -200,9 +200,6 @@
     <t>Capacitor Android Native Bridge Call #4</t>
   </si>
   <si>
-    <t>2026-08-06T10:24:36.611Z</t>
-  </si>
-  <si>
     <t>TC-MOB-005</t>
   </si>
   <si>
@@ -233,6 +230,9 @@
     <t>Capacitor Android Native Bridge Call #9</t>
   </si>
   <si>
+    <t>2026-08-06T13:37:05.081Z</t>
+  </si>
+  <si>
     <t>TC-MOB-010</t>
   </si>
   <si>
@@ -698,6 +698,9 @@
     <t>Biometric Fingerprint / Face Unlock Bridge #4</t>
   </si>
   <si>
+    <t>2026-08-06T13:37:05.082Z</t>
+  </si>
+  <si>
     <t>TC-MOB-075</t>
   </si>
   <si>
@@ -884,9 +887,6 @@
     <t>Biometric Fingerprint / Face Unlock Bridge #35</t>
   </si>
   <si>
-    <t>2026-08-06T10:24:36.612Z</t>
-  </si>
-  <si>
     <t>TC-MOB-106</t>
   </si>
   <si>
@@ -1229,6 +1229,9 @@
     <t>Android Camera &amp; Gallery Permission Flow #17</t>
   </si>
   <si>
+    <t>2026-08-06T13:37:05.083Z</t>
+  </si>
+  <si>
     <t>TC-MOB-158</t>
   </si>
   <si>
@@ -1496,9 +1499,6 @@
     <t>Firebase Cloud Messaging (FCM) Alert Dispatch #24</t>
   </si>
   <si>
-    <t>2026-08-06T10:24:36.613Z</t>
-  </si>
-  <si>
     <t>TC-MOB-200</t>
   </si>
   <si>
@@ -1868,6 +1868,9 @@
     <t>Screen rotated to LANDSCAPE: viewport layout recalculated</t>
   </si>
   <si>
+    <t>2026-08-06T13:37:05.084Z</t>
+  </si>
+  <si>
     <t>TC-MOB-242</t>
   </si>
   <si>
@@ -2016,9 +2019,6 @@
   </si>
   <si>
     <t>Screen Orientation Adaptive Re-layout #25 (LANDSCAPE)</t>
-  </si>
-  <si>
-    <t>2026-08-06T10:24:36.614Z</t>
   </si>
   <si>
     <t>TC-MOB-266</t>
@@ -3045,12 +3045,12 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
@@ -3059,7 +3059,7 @@
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>50</v>
@@ -3077,12 +3077,12 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -3091,7 +3091,7 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>50</v>
@@ -3109,12 +3109,12 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
@@ -3123,7 +3123,7 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>50</v>
@@ -3141,12 +3141,12 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
@@ -3155,7 +3155,7 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>50</v>
@@ -3173,12 +3173,12 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -3187,7 +3187,7 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>50</v>
@@ -3205,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -3237,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -3269,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -3333,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -3365,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -3397,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -3461,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3493,7 +3493,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3525,7 +3525,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3589,7 +3589,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3621,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -3749,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -3781,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3813,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3877,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3909,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3941,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4037,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4069,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -4165,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -4197,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4229,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -4325,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -4357,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -4389,7 +4389,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -4485,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -4517,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -4677,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -4805,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5029,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5061,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5157,7 +5157,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5189,7 +5189,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -5285,12 +5285,12 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
         <v>216</v>
@@ -5299,7 +5299,7 @@
         <v>217</v>
       </c>
       <c r="D76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E76" t="s">
         <v>219</v>
@@ -5317,12 +5317,12 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s">
         <v>216</v>
@@ -5331,7 +5331,7 @@
         <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E77" t="s">
         <v>219</v>
@@ -5349,12 +5349,12 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B78" t="s">
         <v>216</v>
@@ -5363,7 +5363,7 @@
         <v>217</v>
       </c>
       <c r="D78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E78" t="s">
         <v>219</v>
@@ -5381,12 +5381,12 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B79" t="s">
         <v>216</v>
@@ -5395,7 +5395,7 @@
         <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E79" t="s">
         <v>219</v>
@@ -5413,12 +5413,12 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B80" t="s">
         <v>216</v>
@@ -5427,7 +5427,7 @@
         <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E80" t="s">
         <v>219</v>
@@ -5445,12 +5445,12 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B81" t="s">
         <v>216</v>
@@ -5459,7 +5459,7 @@
         <v>217</v>
       </c>
       <c r="D81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E81" t="s">
         <v>219</v>
@@ -5477,12 +5477,12 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B82" t="s">
         <v>216</v>
@@ -5491,7 +5491,7 @@
         <v>217</v>
       </c>
       <c r="D82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E82" t="s">
         <v>219</v>
@@ -5509,12 +5509,12 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B83" t="s">
         <v>216</v>
@@ -5523,7 +5523,7 @@
         <v>217</v>
       </c>
       <c r="D83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E83" t="s">
         <v>219</v>
@@ -5541,12 +5541,12 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B84" t="s">
         <v>216</v>
@@ -5555,7 +5555,7 @@
         <v>217</v>
       </c>
       <c r="D84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E84" t="s">
         <v>219</v>
@@ -5573,12 +5573,12 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B85" t="s">
         <v>216</v>
@@ -5587,7 +5587,7 @@
         <v>217</v>
       </c>
       <c r="D85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E85" t="s">
         <v>219</v>
@@ -5605,12 +5605,12 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B86" t="s">
         <v>216</v>
@@ -5619,7 +5619,7 @@
         <v>217</v>
       </c>
       <c r="D86" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
@@ -5637,12 +5637,12 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B87" t="s">
         <v>216</v>
@@ -5651,7 +5651,7 @@
         <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E87" t="s">
         <v>219</v>
@@ -5669,12 +5669,12 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B88" t="s">
         <v>216</v>
@@ -5683,7 +5683,7 @@
         <v>217</v>
       </c>
       <c r="D88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E88" t="s">
         <v>219</v>
@@ -5701,12 +5701,12 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B89" t="s">
         <v>216</v>
@@ -5715,7 +5715,7 @@
         <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E89" t="s">
         <v>219</v>
@@ -5733,12 +5733,12 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
         <v>216</v>
@@ -5747,7 +5747,7 @@
         <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E90" t="s">
         <v>219</v>
@@ -5765,12 +5765,12 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
         <v>216</v>
@@ -5779,7 +5779,7 @@
         <v>217</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E91" t="s">
         <v>219</v>
@@ -5797,12 +5797,12 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B92" t="s">
         <v>216</v>
@@ -5811,7 +5811,7 @@
         <v>217</v>
       </c>
       <c r="D92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E92" t="s">
         <v>219</v>
@@ -5829,12 +5829,12 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
         <v>216</v>
@@ -5843,7 +5843,7 @@
         <v>217</v>
       </c>
       <c r="D93" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E93" t="s">
         <v>219</v>
@@ -5861,12 +5861,12 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B94" t="s">
         <v>216</v>
@@ -5875,7 +5875,7 @@
         <v>217</v>
       </c>
       <c r="D94" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E94" t="s">
         <v>219</v>
@@ -5893,12 +5893,12 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B95" t="s">
         <v>216</v>
@@ -5907,7 +5907,7 @@
         <v>217</v>
       </c>
       <c r="D95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E95" t="s">
         <v>219</v>
@@ -5925,12 +5925,12 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B96" t="s">
         <v>216</v>
@@ -5939,7 +5939,7 @@
         <v>217</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E96" t="s">
         <v>219</v>
@@ -5957,12 +5957,12 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B97" t="s">
         <v>216</v>
@@ -5971,7 +5971,7 @@
         <v>217</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E97" t="s">
         <v>219</v>
@@ -5989,12 +5989,12 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B98" t="s">
         <v>216</v>
@@ -6003,7 +6003,7 @@
         <v>217</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E98" t="s">
         <v>219</v>
@@ -6021,12 +6021,12 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B99" t="s">
         <v>216</v>
@@ -6035,7 +6035,7 @@
         <v>217</v>
       </c>
       <c r="D99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E99" t="s">
         <v>219</v>
@@ -6053,12 +6053,12 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B100" t="s">
         <v>216</v>
@@ -6067,7 +6067,7 @@
         <v>217</v>
       </c>
       <c r="D100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B101" t="s">
         <v>216</v>
@@ -6099,7 +6099,7 @@
         <v>217</v>
       </c>
       <c r="D101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E101" t="s">
         <v>219</v>
@@ -6117,12 +6117,12 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B102" t="s">
         <v>216</v>
@@ -6131,7 +6131,7 @@
         <v>217</v>
       </c>
       <c r="D102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E102" t="s">
         <v>219</v>
@@ -6149,12 +6149,12 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B103" t="s">
         <v>216</v>
@@ -6163,7 +6163,7 @@
         <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E103" t="s">
         <v>219</v>
@@ -6181,12 +6181,12 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B104" t="s">
         <v>216</v>
@@ -6195,7 +6195,7 @@
         <v>217</v>
       </c>
       <c r="D104" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E104" t="s">
         <v>219</v>
@@ -6213,12 +6213,12 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B105" t="s">
         <v>216</v>
@@ -6227,7 +6227,7 @@
         <v>217</v>
       </c>
       <c r="D105" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E105" t="s">
         <v>219</v>
@@ -6245,12 +6245,12 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>62</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" t="s">
         <v>216</v>
@@ -6259,7 +6259,7 @@
         <v>217</v>
       </c>
       <c r="D106" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E106" t="s">
         <v>219</v>
@@ -6277,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6309,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6341,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -6373,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -6437,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6469,7 +6469,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -6501,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -6533,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -6565,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -6597,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -6629,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -6693,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -6725,7 +6725,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -6789,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -6885,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -6917,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -6949,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -6981,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,7 +7013,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7045,7 +7045,7 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7077,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7109,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7141,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7205,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7237,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7269,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7301,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7333,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7365,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7397,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7429,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7461,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7525,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7557,7 +7557,7 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7589,7 +7589,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7621,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7685,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -7749,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -7845,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -7877,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -7909,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -7941,12 +7941,12 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B159" t="s">
         <v>367</v>
@@ -7955,7 +7955,7 @@
         <v>368</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E159" t="s">
         <v>370</v>
@@ -7973,12 +7973,12 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B160" t="s">
         <v>367</v>
@@ -7987,7 +7987,7 @@
         <v>368</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E160" t="s">
         <v>370</v>
@@ -8005,12 +8005,12 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B161" t="s">
         <v>367</v>
@@ -8019,7 +8019,7 @@
         <v>368</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E161" t="s">
         <v>370</v>
@@ -8037,12 +8037,12 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B162" t="s">
         <v>367</v>
@@ -8051,7 +8051,7 @@
         <v>368</v>
       </c>
       <c r="D162" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E162" t="s">
         <v>370</v>
@@ -8069,12 +8069,12 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B163" t="s">
         <v>367</v>
@@ -8083,7 +8083,7 @@
         <v>368</v>
       </c>
       <c r="D163" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E163" t="s">
         <v>370</v>
@@ -8101,12 +8101,12 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B164" t="s">
         <v>367</v>
@@ -8115,7 +8115,7 @@
         <v>368</v>
       </c>
       <c r="D164" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E164" t="s">
         <v>370</v>
@@ -8133,12 +8133,12 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B165" t="s">
         <v>367</v>
@@ -8147,7 +8147,7 @@
         <v>368</v>
       </c>
       <c r="D165" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E165" t="s">
         <v>370</v>
@@ -8165,12 +8165,12 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B166" t="s">
         <v>367</v>
@@ -8179,7 +8179,7 @@
         <v>368</v>
       </c>
       <c r="D166" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E166" t="s">
         <v>370</v>
@@ -8197,12 +8197,12 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B167" t="s">
         <v>367</v>
@@ -8211,7 +8211,7 @@
         <v>368</v>
       </c>
       <c r="D167" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E167" t="s">
         <v>370</v>
@@ -8229,12 +8229,12 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B168" t="s">
         <v>367</v>
@@ -8243,7 +8243,7 @@
         <v>368</v>
       </c>
       <c r="D168" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E168" t="s">
         <v>370</v>
@@ -8261,12 +8261,12 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B169" t="s">
         <v>367</v>
@@ -8275,7 +8275,7 @@
         <v>368</v>
       </c>
       <c r="D169" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E169" t="s">
         <v>370</v>
@@ -8293,12 +8293,12 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B170" t="s">
         <v>367</v>
@@ -8307,7 +8307,7 @@
         <v>368</v>
       </c>
       <c r="D170" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E170" t="s">
         <v>370</v>
@@ -8325,12 +8325,12 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B171" t="s">
         <v>367</v>
@@ -8339,7 +8339,7 @@
         <v>368</v>
       </c>
       <c r="D171" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E171" t="s">
         <v>370</v>
@@ -8357,12 +8357,12 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B172" t="s">
         <v>367</v>
@@ -8371,7 +8371,7 @@
         <v>368</v>
       </c>
       <c r="D172" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E172" t="s">
         <v>370</v>
@@ -8389,12 +8389,12 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B173" t="s">
         <v>367</v>
@@ -8403,7 +8403,7 @@
         <v>368</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E173" t="s">
         <v>370</v>
@@ -8421,12 +8421,12 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B174" t="s">
         <v>367</v>
@@ -8435,7 +8435,7 @@
         <v>368</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E174" t="s">
         <v>370</v>
@@ -8453,12 +8453,12 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B175" t="s">
         <v>367</v>
@@ -8467,7 +8467,7 @@
         <v>368</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E175" t="s">
         <v>370</v>
@@ -8485,12 +8485,12 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B176" t="s">
         <v>367</v>
@@ -8499,7 +8499,7 @@
         <v>368</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E176" t="s">
         <v>370</v>
@@ -8517,30 +8517,30 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B177" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C177" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E177" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F177" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G177" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>53</v>
@@ -8549,31 +8549,31 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>449</v>
+      </c>
+      <c r="B178" t="s">
+        <v>443</v>
+      </c>
+      <c r="C178" t="s">
+        <v>444</v>
+      </c>
+      <c r="D178" t="s">
+        <v>450</v>
+      </c>
+      <c r="E178" t="s">
+        <v>446</v>
+      </c>
+      <c r="F178" t="s">
+        <v>447</v>
+      </c>
+      <c r="G178" t="s">
         <v>448</v>
       </c>
-      <c r="B178" t="s">
-        <v>442</v>
-      </c>
-      <c r="C178" t="s">
-        <v>443</v>
-      </c>
-      <c r="D178" t="s">
-        <v>449</v>
-      </c>
-      <c r="E178" t="s">
-        <v>445</v>
-      </c>
-      <c r="F178" t="s">
-        <v>446</v>
-      </c>
-      <c r="G178" t="s">
-        <v>447</v>
-      </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
       </c>
@@ -8581,30 +8581,30 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C179" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D179" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E179" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F179" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G179" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
@@ -8613,30 +8613,30 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D180" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E180" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F180" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G180" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
@@ -8645,30 +8645,30 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B181" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D181" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E181" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F181" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G181" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
@@ -8677,30 +8677,30 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B182" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C182" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D182" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F182" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G182" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>53</v>
@@ -8709,30 +8709,30 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B183" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C183" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D183" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G183" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>53</v>
@@ -8741,30 +8741,30 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B184" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C184" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D184" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E184" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
@@ -8773,30 +8773,30 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B185" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C185" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D185" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E185" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F185" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -8805,30 +8805,30 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B186" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D186" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E186" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F186" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G186" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -8837,30 +8837,30 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B187" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C187" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D187" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E187" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F187" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G187" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -8869,30 +8869,30 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B188" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C188" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D188" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E188" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F188" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -8901,30 +8901,30 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B189" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C189" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D189" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E189" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F189" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G189" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -8933,30 +8933,30 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B190" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C190" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D190" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E190" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F190" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G190" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -8965,30 +8965,30 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B191" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C191" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D191" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E191" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F191" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G191" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -8997,30 +8997,30 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B192" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C192" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D192" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E192" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F192" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G192" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9029,30 +9029,30 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B193" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C193" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D193" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E193" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F193" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G193" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9061,30 +9061,30 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B194" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C194" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D194" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E194" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F194" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G194" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9093,30 +9093,30 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B195" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C195" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D195" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E195" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F195" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G195" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9125,30 +9125,30 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B196" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C196" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D196" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E196" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F196" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G196" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9157,30 +9157,30 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B197" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C197" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D197" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E197" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F197" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G197" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9189,30 +9189,30 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B198" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C198" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D198" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E198" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F198" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G198" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9221,30 +9221,30 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B199" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C199" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D199" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E199" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F199" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G199" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9253,30 +9253,30 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B200" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C200" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D200" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E200" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F200" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G200" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9285,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9293,22 +9293,22 @@
         <v>495</v>
       </c>
       <c r="B201" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C201" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D201" t="s">
         <v>496</v>
       </c>
       <c r="E201" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F201" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G201" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9317,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -9325,22 +9325,22 @@
         <v>497</v>
       </c>
       <c r="B202" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C202" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D202" t="s">
         <v>498</v>
       </c>
       <c r="E202" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F202" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G202" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9349,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9357,22 +9357,22 @@
         <v>499</v>
       </c>
       <c r="B203" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C203" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D203" t="s">
         <v>500</v>
       </c>
       <c r="E203" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F203" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G203" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9381,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9389,22 +9389,22 @@
         <v>501</v>
       </c>
       <c r="B204" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C204" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D204" t="s">
         <v>502</v>
       </c>
       <c r="E204" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F204" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G204" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9421,22 +9421,22 @@
         <v>503</v>
       </c>
       <c r="B205" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C205" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D205" t="s">
         <v>504</v>
       </c>
       <c r="E205" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F205" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G205" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9445,7 +9445,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -9453,22 +9453,22 @@
         <v>505</v>
       </c>
       <c r="B206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C206" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D206" t="s">
         <v>506</v>
       </c>
       <c r="E206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F206" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9477,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -9485,22 +9485,22 @@
         <v>507</v>
       </c>
       <c r="B207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D207" t="s">
         <v>508</v>
       </c>
       <c r="E207" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F207" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G207" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9509,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -9517,22 +9517,22 @@
         <v>509</v>
       </c>
       <c r="B208" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D208" t="s">
         <v>510</v>
       </c>
       <c r="E208" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F208" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G208" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9541,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -9549,22 +9549,22 @@
         <v>511</v>
       </c>
       <c r="B209" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C209" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D209" t="s">
         <v>512</v>
       </c>
       <c r="E209" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F209" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G209" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9573,7 +9573,7 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -9581,22 +9581,22 @@
         <v>513</v>
       </c>
       <c r="B210" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C210" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D210" t="s">
         <v>514</v>
       </c>
       <c r="E210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F210" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G210" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -9605,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -9613,22 +9613,22 @@
         <v>515</v>
       </c>
       <c r="B211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C211" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D211" t="s">
         <v>516</v>
       </c>
       <c r="E211" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G211" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -9637,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9669,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -9733,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -9765,7 +9765,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -9797,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -9829,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -9861,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -9893,7 +9893,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -9925,7 +9925,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -9957,7 +9957,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -9989,7 +9989,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -10021,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -10053,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -10117,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -10149,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -10213,7 +10213,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -10245,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -10309,7 +10309,7 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -10373,7 +10373,7 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -10405,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -10437,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -10469,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -10533,7 +10533,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -10565,7 +10565,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -10597,7 +10597,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>494</v>
+        <v>405</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -10629,12 +10629,12 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B243" t="s">
         <v>612</v>
@@ -10643,16 +10643,16 @@
         <v>613</v>
       </c>
       <c r="D243" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E243" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F243" t="s">
         <v>616</v>
       </c>
       <c r="G243" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>53</v>
@@ -10661,12 +10661,12 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B244" t="s">
         <v>612</v>
@@ -10675,7 +10675,7 @@
         <v>613</v>
       </c>
       <c r="D244" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E244" t="s">
         <v>615</v>
@@ -10693,12 +10693,12 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B245" t="s">
         <v>612</v>
@@ -10707,16 +10707,16 @@
         <v>613</v>
       </c>
       <c r="D245" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E245" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F245" t="s">
         <v>616</v>
       </c>
       <c r="G245" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
@@ -10725,12 +10725,12 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B246" t="s">
         <v>612</v>
@@ -10739,7 +10739,7 @@
         <v>613</v>
       </c>
       <c r="D246" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E246" t="s">
         <v>615</v>
@@ -10757,12 +10757,12 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B247" t="s">
         <v>612</v>
@@ -10771,16 +10771,16 @@
         <v>613</v>
       </c>
       <c r="D247" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E247" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F247" t="s">
         <v>616</v>
       </c>
       <c r="G247" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
@@ -10789,12 +10789,12 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B248" t="s">
         <v>612</v>
@@ -10803,7 +10803,7 @@
         <v>613</v>
       </c>
       <c r="D248" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E248" t="s">
         <v>615</v>
@@ -10821,12 +10821,12 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B249" t="s">
         <v>612</v>
@@ -10835,16 +10835,16 @@
         <v>613</v>
       </c>
       <c r="D249" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E249" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F249" t="s">
         <v>616</v>
       </c>
       <c r="G249" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
@@ -10853,12 +10853,12 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B250" t="s">
         <v>612</v>
@@ -10867,7 +10867,7 @@
         <v>613</v>
       </c>
       <c r="D250" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E250" t="s">
         <v>615</v>
@@ -10885,12 +10885,12 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B251" t="s">
         <v>612</v>
@@ -10899,16 +10899,16 @@
         <v>613</v>
       </c>
       <c r="D251" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E251" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F251" t="s">
         <v>616</v>
       </c>
       <c r="G251" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
@@ -10917,12 +10917,12 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B252" t="s">
         <v>612</v>
@@ -10931,7 +10931,7 @@
         <v>613</v>
       </c>
       <c r="D252" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E252" t="s">
         <v>615</v>
@@ -10949,12 +10949,12 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B253" t="s">
         <v>612</v>
@@ -10963,16 +10963,16 @@
         <v>613</v>
       </c>
       <c r="D253" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E253" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F253" t="s">
         <v>616</v>
       </c>
       <c r="G253" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
@@ -10981,12 +10981,12 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B254" t="s">
         <v>612</v>
@@ -10995,7 +10995,7 @@
         <v>613</v>
       </c>
       <c r="D254" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E254" t="s">
         <v>615</v>
@@ -11013,12 +11013,12 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B255" t="s">
         <v>612</v>
@@ -11027,16 +11027,16 @@
         <v>613</v>
       </c>
       <c r="D255" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E255" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F255" t="s">
         <v>616</v>
       </c>
       <c r="G255" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
@@ -11045,12 +11045,12 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B256" t="s">
         <v>612</v>
@@ -11059,7 +11059,7 @@
         <v>613</v>
       </c>
       <c r="D256" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E256" t="s">
         <v>615</v>
@@ -11077,12 +11077,12 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B257" t="s">
         <v>612</v>
@@ -11091,16 +11091,16 @@
         <v>613</v>
       </c>
       <c r="D257" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E257" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F257" t="s">
         <v>616</v>
       </c>
       <c r="G257" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
@@ -11109,12 +11109,12 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B258" t="s">
         <v>612</v>
@@ -11123,7 +11123,7 @@
         <v>613</v>
       </c>
       <c r="D258" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E258" t="s">
         <v>615</v>
@@ -11141,12 +11141,12 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B259" t="s">
         <v>612</v>
@@ -11155,16 +11155,16 @@
         <v>613</v>
       </c>
       <c r="D259" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E259" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F259" t="s">
         <v>616</v>
       </c>
       <c r="G259" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>53</v>
@@ -11173,12 +11173,12 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B260" t="s">
         <v>612</v>
@@ -11187,7 +11187,7 @@
         <v>613</v>
       </c>
       <c r="D260" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E260" t="s">
         <v>615</v>
@@ -11205,12 +11205,12 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B261" t="s">
         <v>612</v>
@@ -11219,16 +11219,16 @@
         <v>613</v>
       </c>
       <c r="D261" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E261" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F261" t="s">
         <v>616</v>
       </c>
       <c r="G261" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
@@ -11237,12 +11237,12 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B262" t="s">
         <v>612</v>
@@ -11251,7 +11251,7 @@
         <v>613</v>
       </c>
       <c r="D262" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E262" t="s">
         <v>615</v>
@@ -11269,12 +11269,12 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B263" t="s">
         <v>612</v>
@@ -11283,16 +11283,16 @@
         <v>613</v>
       </c>
       <c r="D263" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E263" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F263" t="s">
         <v>616</v>
       </c>
       <c r="G263" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
@@ -11301,12 +11301,12 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B264" t="s">
         <v>612</v>
@@ -11315,7 +11315,7 @@
         <v>613</v>
       </c>
       <c r="D264" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E264" t="s">
         <v>615</v>
@@ -11333,12 +11333,12 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B265" t="s">
         <v>612</v>
@@ -11347,16 +11347,16 @@
         <v>613</v>
       </c>
       <c r="D265" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E265" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F265" t="s">
         <v>616</v>
       </c>
       <c r="G265" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
@@ -11365,12 +11365,12 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B266" t="s">
         <v>612</v>
@@ -11379,7 +11379,7 @@
         <v>613</v>
       </c>
       <c r="D266" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E266" t="s">
         <v>615</v>
@@ -11397,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -11414,13 +11414,13 @@
         <v>670</v>
       </c>
       <c r="E267" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F267" t="s">
         <v>616</v>
       </c>
       <c r="G267" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
@@ -11429,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -11461,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -11478,13 +11478,13 @@
         <v>674</v>
       </c>
       <c r="E269" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F269" t="s">
         <v>616</v>
       </c>
       <c r="G269" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
@@ -11493,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -11542,13 +11542,13 @@
         <v>678</v>
       </c>
       <c r="E271" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F271" t="s">
         <v>616</v>
       </c>
       <c r="G271" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
@@ -11557,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -11589,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -11621,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -11653,7 +11653,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -11685,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -11717,7 +11717,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -11749,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -11781,7 +11781,7 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -11813,7 +11813,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -11845,7 +11845,7 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -11877,7 +11877,7 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -11909,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -11941,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -11973,7 +11973,7 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -12005,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -12037,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -12069,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -12101,7 +12101,7 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -12133,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -12165,7 +12165,7 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -12197,7 +12197,7 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -12229,7 +12229,7 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -12261,7 +12261,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -12293,7 +12293,7 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -12325,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -12357,7 +12357,7 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -12389,7 +12389,7 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -12421,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -12453,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -12485,7 +12485,7 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -12517,7 +12517,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/appium-tests/Appium_Test_Report.xlsx
+++ b/appium-tests/Appium_Test_Report.xlsx
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>6/8/2026, 7:39:44 pm</t>
+    <t>7/8/2026, 10:17:36 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-06T14:09:44.487Z</t>
+    <t>2026-08-07T04:47:36.603Z</t>
   </si>
   <si>
     <t>TC-MOB-002</t>
@@ -185,7 +185,7 @@
     <t>Capacitor Android Native Bridge Call #2</t>
   </si>
   <si>
-    <t>2026-08-06T14:09:44.490Z</t>
+    <t>2026-08-07T04:47:36.605Z</t>
   </si>
   <si>
     <t>TC-MOB-003</t>
@@ -320,6 +320,9 @@
     <t>Capacitor Android Native Bridge Call #24</t>
   </si>
   <si>
+    <t>2026-08-07T04:47:36.606Z</t>
+  </si>
+  <si>
     <t>TC-MOB-025</t>
   </si>
   <si>
@@ -572,9 +575,6 @@
     <t>Mobile Touch Gesture Interaction #21 (Pinch In)</t>
   </si>
   <si>
-    <t>2026-08-06T14:09:44.491Z</t>
-  </si>
-  <si>
     <t>TC-MOB-057</t>
   </si>
   <si>
@@ -995,7 +995,7 @@
     <t>Offline Storage Caching &amp; Auto-Sync Engine #16</t>
   </si>
   <si>
-    <t>2026-08-06T14:09:44.492Z</t>
+    <t>2026-08-07T04:47:36.607Z</t>
   </si>
   <si>
     <t>TC-MOB-122</t>
@@ -1763,7 +1763,7 @@
     <t>GPS fix: Lat=15.421, Lon=73.821, accuracy=3.2m</t>
   </si>
   <si>
-    <t>2026-08-06T14:09:44.493Z</t>
+    <t>2026-08-07T04:47:36.608Z</t>
   </si>
   <si>
     <t>TC-MOB-232</t>
@@ -3682,12 +3682,12 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -3696,7 +3696,7 @@
         <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>50</v>
@@ -3714,12 +3714,12 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -3728,7 +3728,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
         <v>50</v>
@@ -3746,12 +3746,12 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -3760,7 +3760,7 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>50</v>
@@ -3778,12 +3778,12 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -3792,7 +3792,7 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>50</v>
@@ -3810,12 +3810,12 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -3824,7 +3824,7 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -3842,12 +3842,12 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -3856,7 +3856,7 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
         <v>50</v>
@@ -3874,12 +3874,12 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -3888,7 +3888,7 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -3906,12 +3906,12 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -3920,7 +3920,7 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>50</v>
@@ -3938,12 +3938,12 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -3952,7 +3952,7 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
         <v>50</v>
@@ -3970,12 +3970,12 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -3984,7 +3984,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
@@ -4002,12 +4002,12 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -4016,7 +4016,7 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
         <v>50</v>
@@ -4034,30 +4034,30 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>53</v>
@@ -4066,30 +4066,30 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>53</v>
@@ -4098,30 +4098,30 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>53</v>
@@ -4130,30 +4130,30 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>53</v>
@@ -4162,30 +4162,30 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>53</v>
@@ -4194,30 +4194,30 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>53</v>
@@ -4226,30 +4226,30 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>53</v>
@@ -4258,30 +4258,30 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>53</v>
@@ -4290,30 +4290,30 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>53</v>
@@ -4322,30 +4322,30 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>53</v>
@@ -4354,30 +4354,30 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>53</v>
@@ -4386,30 +4386,30 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>53</v>
@@ -4418,30 +4418,30 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G49" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>53</v>
@@ -4450,30 +4450,30 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>53</v>
@@ -4482,30 +4482,30 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>53</v>
@@ -4514,30 +4514,30 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>53</v>
@@ -4546,30 +4546,30 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>53</v>
@@ -4578,30 +4578,30 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>53</v>
@@ -4610,30 +4610,30 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>53</v>
@@ -4642,30 +4642,30 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E56" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>53</v>
@@ -4674,30 +4674,30 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>53</v>
@@ -4706,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -4714,22 +4714,22 @@
         <v>187</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D58" t="s">
         <v>188</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G58" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>53</v>
@@ -4738,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -4746,22 +4746,22 @@
         <v>189</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D59" t="s">
         <v>190</v>
       </c>
       <c r="E59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>53</v>
@@ -4770,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -4778,22 +4778,22 @@
         <v>191</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s">
         <v>192</v>
       </c>
       <c r="E60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>53</v>
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -4810,22 +4810,22 @@
         <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
         <v>194</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>53</v>
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -4842,22 +4842,22 @@
         <v>195</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
         <v>196</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>53</v>
@@ -4866,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -4874,22 +4874,22 @@
         <v>197</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
         <v>198</v>
       </c>
       <c r="E63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>53</v>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4906,22 +4906,22 @@
         <v>199</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D64" t="s">
         <v>200</v>
       </c>
       <c r="E64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>53</v>
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4938,22 +4938,22 @@
         <v>201</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
         <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>53</v>
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4970,22 +4970,22 @@
         <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
         <v>204</v>
       </c>
       <c r="E66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G66" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>53</v>
@@ -4994,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5002,22 +5002,22 @@
         <v>205</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D67" t="s">
         <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F67" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>53</v>
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5034,22 +5034,22 @@
         <v>207</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
         <v>208</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>53</v>
@@ -5058,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5066,22 +5066,22 @@
         <v>209</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D69" t="s">
         <v>210</v>
       </c>
       <c r="E69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>53</v>
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5098,22 +5098,22 @@
         <v>211</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
         <v>212</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F70" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>53</v>
@@ -5122,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5130,22 +5130,22 @@
         <v>213</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
         <v>214</v>
       </c>
       <c r="E71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>53</v>
@@ -5154,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5186,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -5218,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -5250,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -5282,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5314,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5346,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5410,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5474,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5538,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5570,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5602,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -5666,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -5762,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -5794,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -5826,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -5922,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -5954,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -5986,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6018,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6050,7 +6050,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -6082,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -6114,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6178,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6210,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6242,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6274,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6306,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -6370,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6402,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -6498,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -6594,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -6626,7 +6626,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -6658,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -6722,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -6754,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">

--- a/appium-tests/Appium_Test_Report.xlsx
+++ b/appium-tests/Appium_Test_Report.xlsx
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:17:36 am</t>
+    <t>7/8/2026, 10:47:55 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T04:47:36.603Z</t>
+    <t>2026-08-07T05:17:55.080Z</t>
   </si>
   <si>
     <t>TC-MOB-002</t>
@@ -185,7 +185,7 @@
     <t>Capacitor Android Native Bridge Call #2</t>
   </si>
   <si>
-    <t>2026-08-07T04:47:36.605Z</t>
+    <t>2026-08-07T05:17:55.083Z</t>
   </si>
   <si>
     <t>TC-MOB-003</t>
@@ -320,9 +320,6 @@
     <t>Capacitor Android Native Bridge Call #24</t>
   </si>
   <si>
-    <t>2026-08-07T04:47:36.606Z</t>
-  </si>
-  <si>
     <t>TC-MOB-025</t>
   </si>
   <si>
@@ -605,6 +602,9 @@
     <t>Mobile Touch Gesture Interaction #26 (Swipe Right)</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:55.084Z</t>
+  </si>
+  <si>
     <t>TC-MOB-062</t>
   </si>
   <si>
@@ -995,9 +995,6 @@
     <t>Offline Storage Caching &amp; Auto-Sync Engine #16</t>
   </si>
   <si>
-    <t>2026-08-07T04:47:36.607Z</t>
-  </si>
-  <si>
     <t>TC-MOB-122</t>
   </si>
   <si>
@@ -1295,6 +1292,9 @@
     <t>Android Camera &amp; Gallery Permission Flow #28</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:55.085Z</t>
+  </si>
+  <si>
     <t>TC-MOB-169</t>
   </si>
   <si>
@@ -1763,9 +1763,6 @@
     <t>GPS fix: Lat=15.421, Lon=73.821, accuracy=3.2m</t>
   </si>
   <si>
-    <t>2026-08-07T04:47:36.608Z</t>
-  </si>
-  <si>
     <t>TC-MOB-232</t>
   </si>
   <si>
@@ -1974,6 +1971,9 @@
   </si>
   <si>
     <t>Screen Orientation Adaptive Re-layout #18 (PORTRAIT)</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:17:55.086Z</t>
   </si>
   <si>
     <t>TC-MOB-259</t>
@@ -3682,12 +3682,12 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -3696,7 +3696,7 @@
         <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
         <v>50</v>
@@ -3714,12 +3714,12 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -3728,7 +3728,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>50</v>
@@ -3746,12 +3746,12 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -3760,7 +3760,7 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
         <v>50</v>
@@ -3778,12 +3778,12 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -3792,7 +3792,7 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>50</v>
@@ -3810,12 +3810,12 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -3824,7 +3824,7 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -3842,12 +3842,12 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -3856,7 +3856,7 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>50</v>
@@ -3874,12 +3874,12 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -3888,7 +3888,7 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -3906,12 +3906,12 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -3920,7 +3920,7 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E33" t="s">
         <v>50</v>
@@ -3938,12 +3938,12 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -3952,7 +3952,7 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
         <v>50</v>
@@ -3970,12 +3970,12 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -3984,7 +3984,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
@@ -4002,12 +4002,12 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -4016,7 +4016,7 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
         <v>50</v>
@@ -4034,31 +4034,31 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s">
         <v>125</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>126</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>127</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>128</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>129</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>130</v>
       </c>
-      <c r="G37" t="s">
-        <v>131</v>
-      </c>
       <c r="H37" s="3" t="s">
         <v>53</v>
       </c>
@@ -4066,31 +4066,31 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" t="s">
         <v>132</v>
       </c>
-      <c r="B38" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>133</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>134</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>135</v>
       </c>
-      <c r="G38" t="s">
-        <v>136</v>
-      </c>
       <c r="H38" s="3" t="s">
         <v>53</v>
       </c>
@@ -4098,31 +4098,31 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" t="s">
         <v>137</v>
       </c>
-      <c r="B39" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>138</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>139</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>140</v>
       </c>
-      <c r="G39" t="s">
-        <v>141</v>
-      </c>
       <c r="H39" s="3" t="s">
         <v>53</v>
       </c>
@@ -4130,31 +4130,31 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" t="s">
         <v>142</v>
       </c>
-      <c r="B40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>143</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>144</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>145</v>
       </c>
-      <c r="G40" t="s">
-        <v>146</v>
-      </c>
       <c r="H40" s="3" t="s">
         <v>53</v>
       </c>
@@ -4162,31 +4162,31 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" t="s">
         <v>147</v>
       </c>
-      <c r="B41" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>148</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>149</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>150</v>
       </c>
-      <c r="G41" t="s">
-        <v>151</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>53</v>
       </c>
@@ -4194,31 +4194,31 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" t="s">
         <v>152</v>
       </c>
-      <c r="B42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>153</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>154</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>155</v>
       </c>
-      <c r="G42" t="s">
-        <v>156</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>53</v>
       </c>
@@ -4226,31 +4226,31 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" t="s">
         <v>157</v>
       </c>
-      <c r="B43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" t="s">
-        <v>127</v>
-      </c>
-      <c r="D43" t="s">
-        <v>158</v>
-      </c>
       <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" t="s">
         <v>129</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>130</v>
       </c>
-      <c r="G43" t="s">
-        <v>131</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>53</v>
       </c>
@@ -4258,31 +4258,31 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" t="s">
         <v>159</v>
       </c>
-      <c r="B44" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" t="s">
-        <v>160</v>
-      </c>
       <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
         <v>134</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>135</v>
       </c>
-      <c r="G44" t="s">
-        <v>136</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>53</v>
       </c>
@@ -4290,31 +4290,31 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" t="s">
         <v>161</v>
       </c>
-      <c r="B45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45" t="s">
-        <v>162</v>
-      </c>
       <c r="E45" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" t="s">
         <v>139</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>140</v>
       </c>
-      <c r="G45" t="s">
-        <v>141</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>53</v>
       </c>
@@ -4322,31 +4322,31 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" t="s">
         <v>163</v>
       </c>
-      <c r="B46" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46" t="s">
-        <v>164</v>
-      </c>
       <c r="E46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F46" t="s">
         <v>144</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>145</v>
       </c>
-      <c r="G46" t="s">
-        <v>146</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>53</v>
       </c>
@@ -4354,31 +4354,31 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s">
         <v>165</v>
       </c>
-      <c r="B47" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" t="s">
-        <v>166</v>
-      </c>
       <c r="E47" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" t="s">
         <v>149</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>150</v>
       </c>
-      <c r="G47" t="s">
-        <v>151</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>53</v>
       </c>
@@ -4386,31 +4386,31 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" t="s">
         <v>167</v>
       </c>
-      <c r="B48" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" t="s">
-        <v>168</v>
-      </c>
       <c r="E48" t="s">
+        <v>153</v>
+      </c>
+      <c r="F48" t="s">
         <v>154</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>155</v>
       </c>
-      <c r="G48" t="s">
-        <v>156</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>53</v>
       </c>
@@ -4418,31 +4418,31 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>168</v>
+      </c>
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" t="s">
         <v>169</v>
       </c>
-      <c r="B49" t="s">
-        <v>126</v>
-      </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" t="s">
-        <v>170</v>
-      </c>
       <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" t="s">
         <v>129</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>130</v>
       </c>
-      <c r="G49" t="s">
-        <v>131</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>53</v>
       </c>
@@ -4450,31 +4450,31 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" t="s">
         <v>171</v>
       </c>
-      <c r="B50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C50" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" t="s">
-        <v>172</v>
-      </c>
       <c r="E50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50" t="s">
         <v>134</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>135</v>
       </c>
-      <c r="G50" t="s">
-        <v>136</v>
-      </c>
       <c r="H50" s="3" t="s">
         <v>53</v>
       </c>
@@ -4482,31 +4482,31 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
         <v>173</v>
       </c>
-      <c r="B51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" t="s">
-        <v>174</v>
-      </c>
       <c r="E51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" t="s">
         <v>139</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>140</v>
       </c>
-      <c r="G51" t="s">
-        <v>141</v>
-      </c>
       <c r="H51" s="3" t="s">
         <v>53</v>
       </c>
@@ -4514,31 +4514,31 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" t="s">
         <v>175</v>
       </c>
-      <c r="B52" t="s">
-        <v>126</v>
-      </c>
-      <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" t="s">
-        <v>176</v>
-      </c>
       <c r="E52" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" t="s">
         <v>144</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>145</v>
       </c>
-      <c r="G52" t="s">
-        <v>146</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>53</v>
       </c>
@@ -4546,31 +4546,31 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
         <v>177</v>
       </c>
-      <c r="B53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
-        <v>178</v>
-      </c>
       <c r="E53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" t="s">
         <v>149</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>150</v>
       </c>
-      <c r="G53" t="s">
-        <v>151</v>
-      </c>
       <c r="H53" s="3" t="s">
         <v>53</v>
       </c>
@@ -4578,31 +4578,31 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>178</v>
+      </c>
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" t="s">
         <v>179</v>
       </c>
-      <c r="B54" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" t="s">
-        <v>180</v>
-      </c>
       <c r="E54" t="s">
+        <v>153</v>
+      </c>
+      <c r="F54" t="s">
         <v>154</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>155</v>
       </c>
-      <c r="G54" t="s">
-        <v>156</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>53</v>
       </c>
@@ -4610,31 +4610,31 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" t="s">
         <v>181</v>
       </c>
-      <c r="B55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" t="s">
-        <v>182</v>
-      </c>
       <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" t="s">
         <v>129</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>130</v>
       </c>
-      <c r="G55" t="s">
-        <v>131</v>
-      </c>
       <c r="H55" s="3" t="s">
         <v>53</v>
       </c>
@@ -4642,31 +4642,31 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
         <v>183</v>
       </c>
-      <c r="B56" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" t="s">
-        <v>184</v>
-      </c>
       <c r="E56" t="s">
+        <v>133</v>
+      </c>
+      <c r="F56" t="s">
         <v>134</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>135</v>
       </c>
-      <c r="G56" t="s">
-        <v>136</v>
-      </c>
       <c r="H56" s="3" t="s">
         <v>53</v>
       </c>
@@ -4674,31 +4674,31 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" t="s">
         <v>185</v>
       </c>
-      <c r="B57" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>186</v>
-      </c>
       <c r="E57" t="s">
+        <v>138</v>
+      </c>
+      <c r="F57" t="s">
         <v>139</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>140</v>
       </c>
-      <c r="G57" t="s">
-        <v>141</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>53</v>
       </c>
@@ -4706,31 +4706,31 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>186</v>
+      </c>
+      <c r="B58" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" t="s">
         <v>187</v>
       </c>
-      <c r="B58" t="s">
-        <v>126</v>
-      </c>
-      <c r="C58" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" t="s">
-        <v>188</v>
-      </c>
       <c r="E58" t="s">
+        <v>143</v>
+      </c>
+      <c r="F58" t="s">
         <v>144</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>145</v>
       </c>
-      <c r="G58" t="s">
-        <v>146</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>53</v>
       </c>
@@ -4738,31 +4738,31 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" t="s">
         <v>189</v>
       </c>
-      <c r="B59" t="s">
-        <v>126</v>
-      </c>
-      <c r="C59" t="s">
-        <v>127</v>
-      </c>
-      <c r="D59" t="s">
-        <v>190</v>
-      </c>
       <c r="E59" t="s">
+        <v>148</v>
+      </c>
+      <c r="F59" t="s">
         <v>149</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>150</v>
       </c>
-      <c r="G59" t="s">
-        <v>151</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>53</v>
       </c>
@@ -4770,31 +4770,31 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>190</v>
+      </c>
+      <c r="B60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" t="s">
         <v>191</v>
       </c>
-      <c r="B60" t="s">
-        <v>126</v>
-      </c>
-      <c r="C60" t="s">
-        <v>127</v>
-      </c>
-      <c r="D60" t="s">
-        <v>192</v>
-      </c>
       <c r="E60" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" t="s">
         <v>154</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>155</v>
       </c>
-      <c r="G60" t="s">
-        <v>156</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>53</v>
       </c>
@@ -4802,31 +4802,31 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" t="s">
         <v>193</v>
       </c>
-      <c r="B61" t="s">
-        <v>126</v>
-      </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" t="s">
-        <v>194</v>
-      </c>
       <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" t="s">
         <v>129</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>130</v>
       </c>
-      <c r="G61" t="s">
-        <v>131</v>
-      </c>
       <c r="H61" s="3" t="s">
         <v>53</v>
       </c>
@@ -4834,39 +4834,39 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>194</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" t="s">
+        <v>126</v>
+      </c>
+      <c r="D62" t="s">
         <v>195</v>
       </c>
-      <c r="B62" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" t="s">
-        <v>127</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
+        <v>133</v>
+      </c>
+      <c r="F62" t="s">
+        <v>134</v>
+      </c>
+      <c r="G62" t="s">
+        <v>135</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
         <v>196</v>
-      </c>
-      <c r="E62" t="s">
-        <v>134</v>
-      </c>
-      <c r="F62" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" t="s">
-        <v>136</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I62">
-        <v>1</v>
-      </c>
-      <c r="J62" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -4874,23 +4874,23 @@
         <v>197</v>
       </c>
       <c r="B63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" t="s">
         <v>126</v>
-      </c>
-      <c r="C63" t="s">
-        <v>127</v>
       </c>
       <c r="D63" t="s">
         <v>198</v>
       </c>
       <c r="E63" t="s">
+        <v>138</v>
+      </c>
+      <c r="F63" t="s">
         <v>139</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>140</v>
       </c>
-      <c r="G63" t="s">
-        <v>141</v>
-      </c>
       <c r="H63" s="3" t="s">
         <v>53</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4906,23 +4906,23 @@
         <v>199</v>
       </c>
       <c r="B64" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" t="s">
         <v>126</v>
-      </c>
-      <c r="C64" t="s">
-        <v>127</v>
       </c>
       <c r="D64" t="s">
         <v>200</v>
       </c>
       <c r="E64" t="s">
+        <v>143</v>
+      </c>
+      <c r="F64" t="s">
         <v>144</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>145</v>
       </c>
-      <c r="G64" t="s">
-        <v>146</v>
-      </c>
       <c r="H64" s="3" t="s">
         <v>53</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4938,23 +4938,23 @@
         <v>201</v>
       </c>
       <c r="B65" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" t="s">
         <v>126</v>
-      </c>
-      <c r="C65" t="s">
-        <v>127</v>
       </c>
       <c r="D65" t="s">
         <v>202</v>
       </c>
       <c r="E65" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" t="s">
         <v>149</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>150</v>
       </c>
-      <c r="G65" t="s">
-        <v>151</v>
-      </c>
       <c r="H65" s="3" t="s">
         <v>53</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4970,23 +4970,23 @@
         <v>203</v>
       </c>
       <c r="B66" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" t="s">
         <v>126</v>
-      </c>
-      <c r="C66" t="s">
-        <v>127</v>
       </c>
       <c r="D66" t="s">
         <v>204</v>
       </c>
       <c r="E66" t="s">
+        <v>153</v>
+      </c>
+      <c r="F66" t="s">
         <v>154</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>155</v>
       </c>
-      <c r="G66" t="s">
-        <v>156</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>53</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5002,23 +5002,23 @@
         <v>205</v>
       </c>
       <c r="B67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" t="s">
         <v>126</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
       </c>
       <c r="D67" t="s">
         <v>206</v>
       </c>
       <c r="E67" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" t="s">
         <v>129</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>130</v>
       </c>
-      <c r="G67" t="s">
-        <v>131</v>
-      </c>
       <c r="H67" s="3" t="s">
         <v>53</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5034,23 +5034,23 @@
         <v>207</v>
       </c>
       <c r="B68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" t="s">
         <v>126</v>
-      </c>
-      <c r="C68" t="s">
-        <v>127</v>
       </c>
       <c r="D68" t="s">
         <v>208</v>
       </c>
       <c r="E68" t="s">
+        <v>133</v>
+      </c>
+      <c r="F68" t="s">
         <v>134</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>135</v>
       </c>
-      <c r="G68" t="s">
-        <v>136</v>
-      </c>
       <c r="H68" s="3" t="s">
         <v>53</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5066,23 +5066,23 @@
         <v>209</v>
       </c>
       <c r="B69" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" t="s">
         <v>126</v>
-      </c>
-      <c r="C69" t="s">
-        <v>127</v>
       </c>
       <c r="D69" t="s">
         <v>210</v>
       </c>
       <c r="E69" t="s">
+        <v>138</v>
+      </c>
+      <c r="F69" t="s">
         <v>139</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>140</v>
       </c>
-      <c r="G69" t="s">
-        <v>141</v>
-      </c>
       <c r="H69" s="3" t="s">
         <v>53</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5098,23 +5098,23 @@
         <v>211</v>
       </c>
       <c r="B70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70" t="s">
         <v>126</v>
-      </c>
-      <c r="C70" t="s">
-        <v>127</v>
       </c>
       <c r="D70" t="s">
         <v>212</v>
       </c>
       <c r="E70" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" t="s">
         <v>144</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>145</v>
       </c>
-      <c r="G70" t="s">
-        <v>146</v>
-      </c>
       <c r="H70" s="3" t="s">
         <v>53</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5130,23 +5130,23 @@
         <v>213</v>
       </c>
       <c r="B71" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" t="s">
         <v>126</v>
-      </c>
-      <c r="C71" t="s">
-        <v>127</v>
       </c>
       <c r="D71" t="s">
         <v>214</v>
       </c>
       <c r="E71" t="s">
+        <v>148</v>
+      </c>
+      <c r="F71" t="s">
         <v>149</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>150</v>
       </c>
-      <c r="G71" t="s">
-        <v>151</v>
-      </c>
       <c r="H71" s="3" t="s">
         <v>53</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5186,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -5218,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -5250,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -5282,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5314,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5346,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5410,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5474,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5538,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5570,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5602,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -5666,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -5762,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -5794,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -5826,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -5922,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -5954,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -5986,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6018,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6050,7 +6050,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -6082,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -6114,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6178,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6210,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6242,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6274,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6306,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -6370,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6402,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -6498,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -6594,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -6626,7 +6626,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -6658,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -6722,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -6754,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -6786,12 +6786,12 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B123" t="s">
         <v>291</v>
@@ -6800,7 +6800,7 @@
         <v>292</v>
       </c>
       <c r="D123" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E123" t="s">
         <v>294</v>
@@ -6818,12 +6818,12 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B124" t="s">
         <v>291</v>
@@ -6832,7 +6832,7 @@
         <v>292</v>
       </c>
       <c r="D124" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E124" t="s">
         <v>294</v>
@@ -6850,12 +6850,12 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B125" t="s">
         <v>291</v>
@@ -6864,7 +6864,7 @@
         <v>292</v>
       </c>
       <c r="D125" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E125" t="s">
         <v>294</v>
@@ -6882,12 +6882,12 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B126" t="s">
         <v>291</v>
@@ -6896,7 +6896,7 @@
         <v>292</v>
       </c>
       <c r="D126" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E126" t="s">
         <v>294</v>
@@ -6914,12 +6914,12 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B127" t="s">
         <v>291</v>
@@ -6928,7 +6928,7 @@
         <v>292</v>
       </c>
       <c r="D127" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E127" t="s">
         <v>294</v>
@@ -6946,12 +6946,12 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B128" t="s">
         <v>291</v>
@@ -6960,7 +6960,7 @@
         <v>292</v>
       </c>
       <c r="D128" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E128" t="s">
         <v>294</v>
@@ -6978,12 +6978,12 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s">
         <v>291</v>
@@ -6992,7 +6992,7 @@
         <v>292</v>
       </c>
       <c r="D129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E129" t="s">
         <v>294</v>
@@ -7010,12 +7010,12 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B130" t="s">
         <v>291</v>
@@ -7024,7 +7024,7 @@
         <v>292</v>
       </c>
       <c r="D130" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E130" t="s">
         <v>294</v>
@@ -7042,12 +7042,12 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B131" t="s">
         <v>291</v>
@@ -7056,7 +7056,7 @@
         <v>292</v>
       </c>
       <c r="D131" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E131" t="s">
         <v>294</v>
@@ -7074,12 +7074,12 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B132" t="s">
         <v>291</v>
@@ -7088,7 +7088,7 @@
         <v>292</v>
       </c>
       <c r="D132" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E132" t="s">
         <v>294</v>
@@ -7106,12 +7106,12 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B133" t="s">
         <v>291</v>
@@ -7120,7 +7120,7 @@
         <v>292</v>
       </c>
       <c r="D133" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E133" t="s">
         <v>294</v>
@@ -7138,12 +7138,12 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B134" t="s">
         <v>291</v>
@@ -7152,7 +7152,7 @@
         <v>292</v>
       </c>
       <c r="D134" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E134" t="s">
         <v>294</v>
@@ -7170,12 +7170,12 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B135" t="s">
         <v>291</v>
@@ -7184,7 +7184,7 @@
         <v>292</v>
       </c>
       <c r="D135" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E135" t="s">
         <v>294</v>
@@ -7202,12 +7202,12 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B136" t="s">
         <v>291</v>
@@ -7216,7 +7216,7 @@
         <v>292</v>
       </c>
       <c r="D136" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E136" t="s">
         <v>294</v>
@@ -7234,12 +7234,12 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B137" t="s">
         <v>291</v>
@@ -7248,7 +7248,7 @@
         <v>292</v>
       </c>
       <c r="D137" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E137" t="s">
         <v>294</v>
@@ -7266,12 +7266,12 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B138" t="s">
         <v>291</v>
@@ -7280,7 +7280,7 @@
         <v>292</v>
       </c>
       <c r="D138" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E138" t="s">
         <v>294</v>
@@ -7298,12 +7298,12 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B139" t="s">
         <v>291</v>
@@ -7312,7 +7312,7 @@
         <v>292</v>
       </c>
       <c r="D139" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E139" t="s">
         <v>294</v>
@@ -7330,12 +7330,12 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B140" t="s">
         <v>291</v>
@@ -7344,7 +7344,7 @@
         <v>292</v>
       </c>
       <c r="D140" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E140" t="s">
         <v>294</v>
@@ -7362,12 +7362,12 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B141" t="s">
         <v>291</v>
@@ -7376,7 +7376,7 @@
         <v>292</v>
       </c>
       <c r="D141" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E141" t="s">
         <v>294</v>
@@ -7394,31 +7394,31 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>365</v>
+      </c>
+      <c r="B142" t="s">
         <v>366</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>367</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>368</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>369</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>370</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>371</v>
       </c>
-      <c r="G142" t="s">
-        <v>372</v>
-      </c>
       <c r="H142" s="3" t="s">
         <v>53</v>
       </c>
@@ -7426,31 +7426,31 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>372</v>
+      </c>
+      <c r="B143" t="s">
+        <v>366</v>
+      </c>
+      <c r="C143" t="s">
+        <v>367</v>
+      </c>
+      <c r="D143" t="s">
         <v>373</v>
       </c>
-      <c r="B143" t="s">
-        <v>367</v>
-      </c>
-      <c r="C143" t="s">
-        <v>368</v>
-      </c>
-      <c r="D143" t="s">
-        <v>374</v>
-      </c>
       <c r="E143" t="s">
+        <v>369</v>
+      </c>
+      <c r="F143" t="s">
         <v>370</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>371</v>
       </c>
-      <c r="G143" t="s">
-        <v>372</v>
-      </c>
       <c r="H143" s="3" t="s">
         <v>53</v>
       </c>
@@ -7458,31 +7458,31 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>374</v>
+      </c>
+      <c r="B144" t="s">
+        <v>366</v>
+      </c>
+      <c r="C144" t="s">
+        <v>367</v>
+      </c>
+      <c r="D144" t="s">
         <v>375</v>
       </c>
-      <c r="B144" t="s">
-        <v>367</v>
-      </c>
-      <c r="C144" t="s">
-        <v>368</v>
-      </c>
-      <c r="D144" t="s">
-        <v>376</v>
-      </c>
       <c r="E144" t="s">
+        <v>369</v>
+      </c>
+      <c r="F144" t="s">
         <v>370</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>371</v>
       </c>
-      <c r="G144" t="s">
-        <v>372</v>
-      </c>
       <c r="H144" s="3" t="s">
         <v>53</v>
       </c>
@@ -7490,31 +7490,31 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>376</v>
+      </c>
+      <c r="B145" t="s">
+        <v>366</v>
+      </c>
+      <c r="C145" t="s">
+        <v>367</v>
+      </c>
+      <c r="D145" t="s">
         <v>377</v>
       </c>
-      <c r="B145" t="s">
-        <v>367</v>
-      </c>
-      <c r="C145" t="s">
-        <v>368</v>
-      </c>
-      <c r="D145" t="s">
-        <v>378</v>
-      </c>
       <c r="E145" t="s">
+        <v>369</v>
+      </c>
+      <c r="F145" t="s">
         <v>370</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>371</v>
       </c>
-      <c r="G145" t="s">
-        <v>372</v>
-      </c>
       <c r="H145" s="3" t="s">
         <v>53</v>
       </c>
@@ -7522,31 +7522,31 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>378</v>
+      </c>
+      <c r="B146" t="s">
+        <v>366</v>
+      </c>
+      <c r="C146" t="s">
+        <v>367</v>
+      </c>
+      <c r="D146" t="s">
         <v>379</v>
       </c>
-      <c r="B146" t="s">
-        <v>367</v>
-      </c>
-      <c r="C146" t="s">
-        <v>368</v>
-      </c>
-      <c r="D146" t="s">
-        <v>380</v>
-      </c>
       <c r="E146" t="s">
+        <v>369</v>
+      </c>
+      <c r="F146" t="s">
         <v>370</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>371</v>
       </c>
-      <c r="G146" t="s">
-        <v>372</v>
-      </c>
       <c r="H146" s="3" t="s">
         <v>53</v>
       </c>
@@ -7554,31 +7554,31 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>380</v>
+      </c>
+      <c r="B147" t="s">
+        <v>366</v>
+      </c>
+      <c r="C147" t="s">
+        <v>367</v>
+      </c>
+      <c r="D147" t="s">
         <v>381</v>
       </c>
-      <c r="B147" t="s">
-        <v>367</v>
-      </c>
-      <c r="C147" t="s">
-        <v>368</v>
-      </c>
-      <c r="D147" t="s">
-        <v>382</v>
-      </c>
       <c r="E147" t="s">
+        <v>369</v>
+      </c>
+      <c r="F147" t="s">
         <v>370</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>371</v>
       </c>
-      <c r="G147" t="s">
-        <v>372</v>
-      </c>
       <c r="H147" s="3" t="s">
         <v>53</v>
       </c>
@@ -7586,31 +7586,31 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>382</v>
+      </c>
+      <c r="B148" t="s">
+        <v>366</v>
+      </c>
+      <c r="C148" t="s">
+        <v>367</v>
+      </c>
+      <c r="D148" t="s">
         <v>383</v>
       </c>
-      <c r="B148" t="s">
-        <v>367</v>
-      </c>
-      <c r="C148" t="s">
-        <v>368</v>
-      </c>
-      <c r="D148" t="s">
-        <v>384</v>
-      </c>
       <c r="E148" t="s">
+        <v>369</v>
+      </c>
+      <c r="F148" t="s">
         <v>370</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>371</v>
       </c>
-      <c r="G148" t="s">
-        <v>372</v>
-      </c>
       <c r="H148" s="3" t="s">
         <v>53</v>
       </c>
@@ -7618,31 +7618,31 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>384</v>
+      </c>
+      <c r="B149" t="s">
+        <v>366</v>
+      </c>
+      <c r="C149" t="s">
+        <v>367</v>
+      </c>
+      <c r="D149" t="s">
         <v>385</v>
       </c>
-      <c r="B149" t="s">
-        <v>367</v>
-      </c>
-      <c r="C149" t="s">
-        <v>368</v>
-      </c>
-      <c r="D149" t="s">
-        <v>386</v>
-      </c>
       <c r="E149" t="s">
+        <v>369</v>
+      </c>
+      <c r="F149" t="s">
         <v>370</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>371</v>
       </c>
-      <c r="G149" t="s">
-        <v>372</v>
-      </c>
       <c r="H149" s="3" t="s">
         <v>53</v>
       </c>
@@ -7650,31 +7650,31 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>386</v>
+      </c>
+      <c r="B150" t="s">
+        <v>366</v>
+      </c>
+      <c r="C150" t="s">
+        <v>367</v>
+      </c>
+      <c r="D150" t="s">
         <v>387</v>
       </c>
-      <c r="B150" t="s">
-        <v>367</v>
-      </c>
-      <c r="C150" t="s">
-        <v>368</v>
-      </c>
-      <c r="D150" t="s">
-        <v>388</v>
-      </c>
       <c r="E150" t="s">
+        <v>369</v>
+      </c>
+      <c r="F150" t="s">
         <v>370</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>371</v>
       </c>
-      <c r="G150" t="s">
-        <v>372</v>
-      </c>
       <c r="H150" s="3" t="s">
         <v>53</v>
       </c>
@@ -7682,31 +7682,31 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>388</v>
+      </c>
+      <c r="B151" t="s">
+        <v>366</v>
+      </c>
+      <c r="C151" t="s">
+        <v>367</v>
+      </c>
+      <c r="D151" t="s">
         <v>389</v>
       </c>
-      <c r="B151" t="s">
-        <v>367</v>
-      </c>
-      <c r="C151" t="s">
-        <v>368</v>
-      </c>
-      <c r="D151" t="s">
-        <v>390</v>
-      </c>
       <c r="E151" t="s">
+        <v>369</v>
+      </c>
+      <c r="F151" t="s">
         <v>370</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>371</v>
       </c>
-      <c r="G151" t="s">
-        <v>372</v>
-      </c>
       <c r="H151" s="3" t="s">
         <v>53</v>
       </c>
@@ -7714,31 +7714,31 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>390</v>
+      </c>
+      <c r="B152" t="s">
+        <v>366</v>
+      </c>
+      <c r="C152" t="s">
+        <v>367</v>
+      </c>
+      <c r="D152" t="s">
         <v>391</v>
       </c>
-      <c r="B152" t="s">
-        <v>367</v>
-      </c>
-      <c r="C152" t="s">
-        <v>368</v>
-      </c>
-      <c r="D152" t="s">
-        <v>392</v>
-      </c>
       <c r="E152" t="s">
+        <v>369</v>
+      </c>
+      <c r="F152" t="s">
         <v>370</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>371</v>
       </c>
-      <c r="G152" t="s">
-        <v>372</v>
-      </c>
       <c r="H152" s="3" t="s">
         <v>53</v>
       </c>
@@ -7746,31 +7746,31 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>392</v>
+      </c>
+      <c r="B153" t="s">
+        <v>366</v>
+      </c>
+      <c r="C153" t="s">
+        <v>367</v>
+      </c>
+      <c r="D153" t="s">
         <v>393</v>
       </c>
-      <c r="B153" t="s">
-        <v>367</v>
-      </c>
-      <c r="C153" t="s">
-        <v>368</v>
-      </c>
-      <c r="D153" t="s">
-        <v>394</v>
-      </c>
       <c r="E153" t="s">
+        <v>369</v>
+      </c>
+      <c r="F153" t="s">
         <v>370</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>371</v>
       </c>
-      <c r="G153" t="s">
-        <v>372</v>
-      </c>
       <c r="H153" s="3" t="s">
         <v>53</v>
       </c>
@@ -7778,31 +7778,31 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>394</v>
+      </c>
+      <c r="B154" t="s">
+        <v>366</v>
+      </c>
+      <c r="C154" t="s">
+        <v>367</v>
+      </c>
+      <c r="D154" t="s">
         <v>395</v>
       </c>
-      <c r="B154" t="s">
-        <v>367</v>
-      </c>
-      <c r="C154" t="s">
-        <v>368</v>
-      </c>
-      <c r="D154" t="s">
-        <v>396</v>
-      </c>
       <c r="E154" t="s">
+        <v>369</v>
+      </c>
+      <c r="F154" t="s">
         <v>370</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>371</v>
       </c>
-      <c r="G154" t="s">
-        <v>372</v>
-      </c>
       <c r="H154" s="3" t="s">
         <v>53</v>
       </c>
@@ -7810,31 +7810,31 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>396</v>
+      </c>
+      <c r="B155" t="s">
+        <v>366</v>
+      </c>
+      <c r="C155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D155" t="s">
         <v>397</v>
       </c>
-      <c r="B155" t="s">
-        <v>367</v>
-      </c>
-      <c r="C155" t="s">
-        <v>368</v>
-      </c>
-      <c r="D155" t="s">
-        <v>398</v>
-      </c>
       <c r="E155" t="s">
+        <v>369</v>
+      </c>
+      <c r="F155" t="s">
         <v>370</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>371</v>
       </c>
-      <c r="G155" t="s">
-        <v>372</v>
-      </c>
       <c r="H155" s="3" t="s">
         <v>53</v>
       </c>
@@ -7842,31 +7842,31 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>398</v>
+      </c>
+      <c r="B156" t="s">
+        <v>366</v>
+      </c>
+      <c r="C156" t="s">
+        <v>367</v>
+      </c>
+      <c r="D156" t="s">
         <v>399</v>
       </c>
-      <c r="B156" t="s">
-        <v>367</v>
-      </c>
-      <c r="C156" t="s">
-        <v>368</v>
-      </c>
-      <c r="D156" t="s">
-        <v>400</v>
-      </c>
       <c r="E156" t="s">
+        <v>369</v>
+      </c>
+      <c r="F156" t="s">
         <v>370</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>371</v>
       </c>
-      <c r="G156" t="s">
-        <v>372</v>
-      </c>
       <c r="H156" s="3" t="s">
         <v>53</v>
       </c>
@@ -7874,31 +7874,31 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>400</v>
+      </c>
+      <c r="B157" t="s">
+        <v>366</v>
+      </c>
+      <c r="C157" t="s">
+        <v>367</v>
+      </c>
+      <c r="D157" t="s">
         <v>401</v>
       </c>
-      <c r="B157" t="s">
-        <v>367</v>
-      </c>
-      <c r="C157" t="s">
-        <v>368</v>
-      </c>
-      <c r="D157" t="s">
-        <v>402</v>
-      </c>
       <c r="E157" t="s">
+        <v>369</v>
+      </c>
+      <c r="F157" t="s">
         <v>370</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>371</v>
       </c>
-      <c r="G157" t="s">
-        <v>372</v>
-      </c>
       <c r="H157" s="3" t="s">
         <v>53</v>
       </c>
@@ -7906,31 +7906,31 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>402</v>
+      </c>
+      <c r="B158" t="s">
+        <v>366</v>
+      </c>
+      <c r="C158" t="s">
+        <v>367</v>
+      </c>
+      <c r="D158" t="s">
         <v>403</v>
       </c>
-      <c r="B158" t="s">
-        <v>367</v>
-      </c>
-      <c r="C158" t="s">
-        <v>368</v>
-      </c>
-      <c r="D158" t="s">
-        <v>404</v>
-      </c>
       <c r="E158" t="s">
+        <v>369</v>
+      </c>
+      <c r="F158" t="s">
         <v>370</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>371</v>
       </c>
-      <c r="G158" t="s">
-        <v>372</v>
-      </c>
       <c r="H158" s="3" t="s">
         <v>53</v>
       </c>
@@ -7938,31 +7938,31 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>404</v>
+      </c>
+      <c r="B159" t="s">
+        <v>366</v>
+      </c>
+      <c r="C159" t="s">
+        <v>367</v>
+      </c>
+      <c r="D159" t="s">
         <v>405</v>
       </c>
-      <c r="B159" t="s">
-        <v>367</v>
-      </c>
-      <c r="C159" t="s">
-        <v>368</v>
-      </c>
-      <c r="D159" t="s">
-        <v>406</v>
-      </c>
       <c r="E159" t="s">
+        <v>369</v>
+      </c>
+      <c r="F159" t="s">
         <v>370</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>371</v>
       </c>
-      <c r="G159" t="s">
-        <v>372</v>
-      </c>
       <c r="H159" s="3" t="s">
         <v>53</v>
       </c>
@@ -7970,31 +7970,31 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>406</v>
+      </c>
+      <c r="B160" t="s">
+        <v>366</v>
+      </c>
+      <c r="C160" t="s">
+        <v>367</v>
+      </c>
+      <c r="D160" t="s">
         <v>407</v>
       </c>
-      <c r="B160" t="s">
-        <v>367</v>
-      </c>
-      <c r="C160" t="s">
-        <v>368</v>
-      </c>
-      <c r="D160" t="s">
-        <v>408</v>
-      </c>
       <c r="E160" t="s">
+        <v>369</v>
+      </c>
+      <c r="F160" t="s">
         <v>370</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>371</v>
       </c>
-      <c r="G160" t="s">
-        <v>372</v>
-      </c>
       <c r="H160" s="3" t="s">
         <v>53</v>
       </c>
@@ -8002,31 +8002,31 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>408</v>
+      </c>
+      <c r="B161" t="s">
+        <v>366</v>
+      </c>
+      <c r="C161" t="s">
+        <v>367</v>
+      </c>
+      <c r="D161" t="s">
         <v>409</v>
       </c>
-      <c r="B161" t="s">
-        <v>367</v>
-      </c>
-      <c r="C161" t="s">
-        <v>368</v>
-      </c>
-      <c r="D161" t="s">
-        <v>410</v>
-      </c>
       <c r="E161" t="s">
+        <v>369</v>
+      </c>
+      <c r="F161" t="s">
         <v>370</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>371</v>
       </c>
-      <c r="G161" t="s">
-        <v>372</v>
-      </c>
       <c r="H161" s="3" t="s">
         <v>53</v>
       </c>
@@ -8034,31 +8034,31 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>410</v>
+      </c>
+      <c r="B162" t="s">
+        <v>366</v>
+      </c>
+      <c r="C162" t="s">
+        <v>367</v>
+      </c>
+      <c r="D162" t="s">
         <v>411</v>
       </c>
-      <c r="B162" t="s">
-        <v>367</v>
-      </c>
-      <c r="C162" t="s">
-        <v>368</v>
-      </c>
-      <c r="D162" t="s">
-        <v>412</v>
-      </c>
       <c r="E162" t="s">
+        <v>369</v>
+      </c>
+      <c r="F162" t="s">
         <v>370</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>371</v>
       </c>
-      <c r="G162" t="s">
-        <v>372</v>
-      </c>
       <c r="H162" s="3" t="s">
         <v>53</v>
       </c>
@@ -8066,31 +8066,31 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>412</v>
+      </c>
+      <c r="B163" t="s">
+        <v>366</v>
+      </c>
+      <c r="C163" t="s">
+        <v>367</v>
+      </c>
+      <c r="D163" t="s">
         <v>413</v>
       </c>
-      <c r="B163" t="s">
-        <v>367</v>
-      </c>
-      <c r="C163" t="s">
-        <v>368</v>
-      </c>
-      <c r="D163" t="s">
-        <v>414</v>
-      </c>
       <c r="E163" t="s">
+        <v>369</v>
+      </c>
+      <c r="F163" t="s">
         <v>370</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>371</v>
       </c>
-      <c r="G163" t="s">
-        <v>372</v>
-      </c>
       <c r="H163" s="3" t="s">
         <v>53</v>
       </c>
@@ -8098,31 +8098,31 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>414</v>
+      </c>
+      <c r="B164" t="s">
+        <v>366</v>
+      </c>
+      <c r="C164" t="s">
+        <v>367</v>
+      </c>
+      <c r="D164" t="s">
         <v>415</v>
       </c>
-      <c r="B164" t="s">
-        <v>367</v>
-      </c>
-      <c r="C164" t="s">
-        <v>368</v>
-      </c>
-      <c r="D164" t="s">
-        <v>416</v>
-      </c>
       <c r="E164" t="s">
+        <v>369</v>
+      </c>
+      <c r="F164" t="s">
         <v>370</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>371</v>
       </c>
-      <c r="G164" t="s">
-        <v>372</v>
-      </c>
       <c r="H164" s="3" t="s">
         <v>53</v>
       </c>
@@ -8130,31 +8130,31 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>416</v>
+      </c>
+      <c r="B165" t="s">
+        <v>366</v>
+      </c>
+      <c r="C165" t="s">
+        <v>367</v>
+      </c>
+      <c r="D165" t="s">
         <v>417</v>
       </c>
-      <c r="B165" t="s">
-        <v>367</v>
-      </c>
-      <c r="C165" t="s">
-        <v>368</v>
-      </c>
-      <c r="D165" t="s">
-        <v>418</v>
-      </c>
       <c r="E165" t="s">
+        <v>369</v>
+      </c>
+      <c r="F165" t="s">
         <v>370</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>371</v>
       </c>
-      <c r="G165" t="s">
-        <v>372</v>
-      </c>
       <c r="H165" s="3" t="s">
         <v>53</v>
       </c>
@@ -8162,31 +8162,31 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>418</v>
+      </c>
+      <c r="B166" t="s">
+        <v>366</v>
+      </c>
+      <c r="C166" t="s">
+        <v>367</v>
+      </c>
+      <c r="D166" t="s">
         <v>419</v>
       </c>
-      <c r="B166" t="s">
-        <v>367</v>
-      </c>
-      <c r="C166" t="s">
-        <v>368</v>
-      </c>
-      <c r="D166" t="s">
-        <v>420</v>
-      </c>
       <c r="E166" t="s">
+        <v>369</v>
+      </c>
+      <c r="F166" t="s">
         <v>370</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>371</v>
       </c>
-      <c r="G166" t="s">
-        <v>372</v>
-      </c>
       <c r="H166" s="3" t="s">
         <v>53</v>
       </c>
@@ -8194,31 +8194,31 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>420</v>
+      </c>
+      <c r="B167" t="s">
+        <v>366</v>
+      </c>
+      <c r="C167" t="s">
+        <v>367</v>
+      </c>
+      <c r="D167" t="s">
         <v>421</v>
       </c>
-      <c r="B167" t="s">
-        <v>367</v>
-      </c>
-      <c r="C167" t="s">
-        <v>368</v>
-      </c>
-      <c r="D167" t="s">
-        <v>422</v>
-      </c>
       <c r="E167" t="s">
+        <v>369</v>
+      </c>
+      <c r="F167" t="s">
         <v>370</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>371</v>
       </c>
-      <c r="G167" t="s">
-        <v>372</v>
-      </c>
       <c r="H167" s="3" t="s">
         <v>53</v>
       </c>
@@ -8226,31 +8226,31 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>422</v>
+      </c>
+      <c r="B168" t="s">
+        <v>366</v>
+      </c>
+      <c r="C168" t="s">
+        <v>367</v>
+      </c>
+      <c r="D168" t="s">
         <v>423</v>
       </c>
-      <c r="B168" t="s">
-        <v>367</v>
-      </c>
-      <c r="C168" t="s">
-        <v>368</v>
-      </c>
-      <c r="D168" t="s">
-        <v>424</v>
-      </c>
       <c r="E168" t="s">
+        <v>369</v>
+      </c>
+      <c r="F168" t="s">
         <v>370</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>371</v>
       </c>
-      <c r="G168" t="s">
-        <v>372</v>
-      </c>
       <c r="H168" s="3" t="s">
         <v>53</v>
       </c>
@@ -8258,39 +8258,39 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>424</v>
+      </c>
+      <c r="B169" t="s">
+        <v>366</v>
+      </c>
+      <c r="C169" t="s">
+        <v>367</v>
+      </c>
+      <c r="D169" t="s">
         <v>425</v>
       </c>
-      <c r="B169" t="s">
-        <v>367</v>
-      </c>
-      <c r="C169" t="s">
-        <v>368</v>
-      </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
+        <v>369</v>
+      </c>
+      <c r="F169" t="s">
+        <v>370</v>
+      </c>
+      <c r="G169" t="s">
+        <v>371</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169" t="s">
         <v>426</v>
-      </c>
-      <c r="E169" t="s">
-        <v>370</v>
-      </c>
-      <c r="F169" t="s">
-        <v>371</v>
-      </c>
-      <c r="G169" t="s">
-        <v>372</v>
-      </c>
-      <c r="H169" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I169">
-        <v>1</v>
-      </c>
-      <c r="J169" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8298,23 +8298,23 @@
         <v>427</v>
       </c>
       <c r="B170" t="s">
+        <v>366</v>
+      </c>
+      <c r="C170" t="s">
         <v>367</v>
-      </c>
-      <c r="C170" t="s">
-        <v>368</v>
       </c>
       <c r="D170" t="s">
         <v>428</v>
       </c>
       <c r="E170" t="s">
+        <v>369</v>
+      </c>
+      <c r="F170" t="s">
         <v>370</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>371</v>
       </c>
-      <c r="G170" t="s">
-        <v>372</v>
-      </c>
       <c r="H170" s="3" t="s">
         <v>53</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8330,23 +8330,23 @@
         <v>429</v>
       </c>
       <c r="B171" t="s">
+        <v>366</v>
+      </c>
+      <c r="C171" t="s">
         <v>367</v>
-      </c>
-      <c r="C171" t="s">
-        <v>368</v>
       </c>
       <c r="D171" t="s">
         <v>430</v>
       </c>
       <c r="E171" t="s">
+        <v>369</v>
+      </c>
+      <c r="F171" t="s">
         <v>370</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>371</v>
       </c>
-      <c r="G171" t="s">
-        <v>372</v>
-      </c>
       <c r="H171" s="3" t="s">
         <v>53</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8362,23 +8362,23 @@
         <v>431</v>
       </c>
       <c r="B172" t="s">
+        <v>366</v>
+      </c>
+      <c r="C172" t="s">
         <v>367</v>
-      </c>
-      <c r="C172" t="s">
-        <v>368</v>
       </c>
       <c r="D172" t="s">
         <v>432</v>
       </c>
       <c r="E172" t="s">
+        <v>369</v>
+      </c>
+      <c r="F172" t="s">
         <v>370</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>371</v>
       </c>
-      <c r="G172" t="s">
-        <v>372</v>
-      </c>
       <c r="H172" s="3" t="s">
         <v>53</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8394,23 +8394,23 @@
         <v>433</v>
       </c>
       <c r="B173" t="s">
+        <v>366</v>
+      </c>
+      <c r="C173" t="s">
         <v>367</v>
-      </c>
-      <c r="C173" t="s">
-        <v>368</v>
       </c>
       <c r="D173" t="s">
         <v>434</v>
       </c>
       <c r="E173" t="s">
+        <v>369</v>
+      </c>
+      <c r="F173" t="s">
         <v>370</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>371</v>
       </c>
-      <c r="G173" t="s">
-        <v>372</v>
-      </c>
       <c r="H173" s="3" t="s">
         <v>53</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8426,23 +8426,23 @@
         <v>435</v>
       </c>
       <c r="B174" t="s">
+        <v>366</v>
+      </c>
+      <c r="C174" t="s">
         <v>367</v>
-      </c>
-      <c r="C174" t="s">
-        <v>368</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
       </c>
       <c r="E174" t="s">
+        <v>369</v>
+      </c>
+      <c r="F174" t="s">
         <v>370</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>371</v>
       </c>
-      <c r="G174" t="s">
-        <v>372</v>
-      </c>
       <c r="H174" s="3" t="s">
         <v>53</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8458,23 +8458,23 @@
         <v>437</v>
       </c>
       <c r="B175" t="s">
+        <v>366</v>
+      </c>
+      <c r="C175" t="s">
         <v>367</v>
-      </c>
-      <c r="C175" t="s">
-        <v>368</v>
       </c>
       <c r="D175" t="s">
         <v>438</v>
       </c>
       <c r="E175" t="s">
+        <v>369</v>
+      </c>
+      <c r="F175" t="s">
         <v>370</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>371</v>
       </c>
-      <c r="G175" t="s">
-        <v>372</v>
-      </c>
       <c r="H175" s="3" t="s">
         <v>53</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8490,23 +8490,23 @@
         <v>439</v>
       </c>
       <c r="B176" t="s">
+        <v>366</v>
+      </c>
+      <c r="C176" t="s">
         <v>367</v>
-      </c>
-      <c r="C176" t="s">
-        <v>368</v>
       </c>
       <c r="D176" t="s">
         <v>440</v>
       </c>
       <c r="E176" t="s">
+        <v>369</v>
+      </c>
+      <c r="F176" t="s">
         <v>370</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>371</v>
       </c>
-      <c r="G176" t="s">
-        <v>372</v>
-      </c>
       <c r="H176" s="3" t="s">
         <v>53</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -8546,7 +8546,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -8578,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -8610,7 +8610,7 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -8706,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -8738,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -8770,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -8802,7 +8802,7 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -8834,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -8866,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -8930,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -8994,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -9026,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -9058,7 +9058,7 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -9090,7 +9090,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -9122,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -9154,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -9186,7 +9186,7 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -9218,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -9250,7 +9250,7 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -9282,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9314,7 +9314,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9378,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9410,7 +9410,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9442,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -9474,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -9538,7 +9538,7 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -9570,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -9602,7 +9602,7 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9666,7 +9666,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -9730,7 +9730,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -9762,7 +9762,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -9794,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -9826,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -9858,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -9890,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -9922,7 +9922,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -9986,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -10018,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -10050,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -10082,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -10114,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -10146,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -10178,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -10210,7 +10210,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -10242,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -10274,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -10306,12 +10306,12 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B233" t="s">
         <v>517</v>
@@ -10320,7 +10320,7 @@
         <v>518</v>
       </c>
       <c r="D233" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E233" t="s">
         <v>520</v>
@@ -10329,7 +10329,7 @@
         <v>521</v>
       </c>
       <c r="G233" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
@@ -10338,12 +10338,12 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B234" t="s">
         <v>517</v>
@@ -10352,7 +10352,7 @@
         <v>518</v>
       </c>
       <c r="D234" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E234" t="s">
         <v>520</v>
@@ -10361,7 +10361,7 @@
         <v>521</v>
       </c>
       <c r="G234" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
@@ -10370,12 +10370,12 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B235" t="s">
         <v>517</v>
@@ -10384,7 +10384,7 @@
         <v>518</v>
       </c>
       <c r="D235" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E235" t="s">
         <v>520</v>
@@ -10393,7 +10393,7 @@
         <v>521</v>
       </c>
       <c r="G235" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
@@ -10402,12 +10402,12 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B236" t="s">
         <v>517</v>
@@ -10416,7 +10416,7 @@
         <v>518</v>
       </c>
       <c r="D236" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E236" t="s">
         <v>520</v>
@@ -10425,7 +10425,7 @@
         <v>521</v>
       </c>
       <c r="G236" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
@@ -10434,12 +10434,12 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B237" t="s">
         <v>517</v>
@@ -10448,7 +10448,7 @@
         <v>518</v>
       </c>
       <c r="D237" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E237" t="s">
         <v>520</v>
@@ -10457,7 +10457,7 @@
         <v>521</v>
       </c>
       <c r="G237" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>53</v>
@@ -10466,12 +10466,12 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B238" t="s">
         <v>517</v>
@@ -10480,7 +10480,7 @@
         <v>518</v>
       </c>
       <c r="D238" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E238" t="s">
         <v>520</v>
@@ -10489,7 +10489,7 @@
         <v>521</v>
       </c>
       <c r="G238" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
@@ -10498,12 +10498,12 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B239" t="s">
         <v>517</v>
@@ -10512,7 +10512,7 @@
         <v>518</v>
       </c>
       <c r="D239" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E239" t="s">
         <v>520</v>
@@ -10521,7 +10521,7 @@
         <v>521</v>
       </c>
       <c r="G239" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>53</v>
@@ -10530,12 +10530,12 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B240" t="s">
         <v>517</v>
@@ -10544,7 +10544,7 @@
         <v>518</v>
       </c>
       <c r="D240" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E240" t="s">
         <v>520</v>
@@ -10553,7 +10553,7 @@
         <v>521</v>
       </c>
       <c r="G240" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>53</v>
@@ -10562,12 +10562,12 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B241" t="s">
         <v>517</v>
@@ -10576,7 +10576,7 @@
         <v>518</v>
       </c>
       <c r="D241" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E241" t="s">
         <v>520</v>
@@ -10585,7 +10585,7 @@
         <v>521</v>
       </c>
       <c r="G241" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>53</v>
@@ -10594,31 +10594,31 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>610</v>
+      </c>
+      <c r="B242" t="s">
         <v>611</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" t="s">
         <v>612</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D242" t="s">
         <v>613</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
         <v>614</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>615</v>
       </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>616</v>
       </c>
-      <c r="G242" t="s">
-        <v>617</v>
-      </c>
       <c r="H242" s="3" t="s">
         <v>53</v>
       </c>
@@ -10626,31 +10626,31 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>617</v>
+      </c>
+      <c r="B243" t="s">
+        <v>611</v>
+      </c>
+      <c r="C243" t="s">
+        <v>612</v>
+      </c>
+      <c r="D243" t="s">
         <v>618</v>
       </c>
-      <c r="B243" t="s">
-        <v>612</v>
-      </c>
-      <c r="C243" t="s">
-        <v>613</v>
-      </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
         <v>619</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
+        <v>615</v>
+      </c>
+      <c r="G243" t="s">
         <v>620</v>
       </c>
-      <c r="F243" t="s">
-        <v>616</v>
-      </c>
-      <c r="G243" t="s">
-        <v>621</v>
-      </c>
       <c r="H243" s="3" t="s">
         <v>53</v>
       </c>
@@ -10658,31 +10658,31 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>621</v>
+      </c>
+      <c r="B244" t="s">
+        <v>611</v>
+      </c>
+      <c r="C244" t="s">
+        <v>612</v>
+      </c>
+      <c r="D244" t="s">
         <v>622</v>
       </c>
-      <c r="B244" t="s">
-        <v>612</v>
-      </c>
-      <c r="C244" t="s">
-        <v>613</v>
-      </c>
-      <c r="D244" t="s">
-        <v>623</v>
-      </c>
       <c r="E244" t="s">
+        <v>614</v>
+      </c>
+      <c r="F244" t="s">
         <v>615</v>
       </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>616</v>
       </c>
-      <c r="G244" t="s">
-        <v>617</v>
-      </c>
       <c r="H244" s="3" t="s">
         <v>53</v>
       </c>
@@ -10690,31 +10690,31 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>623</v>
+      </c>
+      <c r="B245" t="s">
+        <v>611</v>
+      </c>
+      <c r="C245" t="s">
+        <v>612</v>
+      </c>
+      <c r="D245" t="s">
         <v>624</v>
       </c>
-      <c r="B245" t="s">
-        <v>612</v>
-      </c>
-      <c r="C245" t="s">
-        <v>613</v>
-      </c>
-      <c r="D245" t="s">
-        <v>625</v>
-      </c>
       <c r="E245" t="s">
+        <v>619</v>
+      </c>
+      <c r="F245" t="s">
+        <v>615</v>
+      </c>
+      <c r="G245" t="s">
         <v>620</v>
       </c>
-      <c r="F245" t="s">
-        <v>616</v>
-      </c>
-      <c r="G245" t="s">
-        <v>621</v>
-      </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
       </c>
@@ -10722,31 +10722,31 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>625</v>
+      </c>
+      <c r="B246" t="s">
+        <v>611</v>
+      </c>
+      <c r="C246" t="s">
+        <v>612</v>
+      </c>
+      <c r="D246" t="s">
         <v>626</v>
       </c>
-      <c r="B246" t="s">
-        <v>612</v>
-      </c>
-      <c r="C246" t="s">
-        <v>613</v>
-      </c>
-      <c r="D246" t="s">
-        <v>627</v>
-      </c>
       <c r="E246" t="s">
+        <v>614</v>
+      </c>
+      <c r="F246" t="s">
         <v>615</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>616</v>
       </c>
-      <c r="G246" t="s">
-        <v>617</v>
-      </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
       </c>
@@ -10754,31 +10754,31 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>627</v>
+      </c>
+      <c r="B247" t="s">
+        <v>611</v>
+      </c>
+      <c r="C247" t="s">
+        <v>612</v>
+      </c>
+      <c r="D247" t="s">
         <v>628</v>
       </c>
-      <c r="B247" t="s">
-        <v>612</v>
-      </c>
-      <c r="C247" t="s">
-        <v>613</v>
-      </c>
-      <c r="D247" t="s">
-        <v>629</v>
-      </c>
       <c r="E247" t="s">
+        <v>619</v>
+      </c>
+      <c r="F247" t="s">
+        <v>615</v>
+      </c>
+      <c r="G247" t="s">
         <v>620</v>
       </c>
-      <c r="F247" t="s">
-        <v>616</v>
-      </c>
-      <c r="G247" t="s">
-        <v>621</v>
-      </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
       </c>
@@ -10786,31 +10786,31 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>629</v>
+      </c>
+      <c r="B248" t="s">
+        <v>611</v>
+      </c>
+      <c r="C248" t="s">
+        <v>612</v>
+      </c>
+      <c r="D248" t="s">
         <v>630</v>
       </c>
-      <c r="B248" t="s">
-        <v>612</v>
-      </c>
-      <c r="C248" t="s">
-        <v>613</v>
-      </c>
-      <c r="D248" t="s">
-        <v>631</v>
-      </c>
       <c r="E248" t="s">
+        <v>614</v>
+      </c>
+      <c r="F248" t="s">
         <v>615</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
         <v>616</v>
       </c>
-      <c r="G248" t="s">
-        <v>617</v>
-      </c>
       <c r="H248" s="3" t="s">
         <v>53</v>
       </c>
@@ -10818,31 +10818,31 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>631</v>
+      </c>
+      <c r="B249" t="s">
+        <v>611</v>
+      </c>
+      <c r="C249" t="s">
+        <v>612</v>
+      </c>
+      <c r="D249" t="s">
         <v>632</v>
       </c>
-      <c r="B249" t="s">
-        <v>612</v>
-      </c>
-      <c r="C249" t="s">
-        <v>613</v>
-      </c>
-      <c r="D249" t="s">
-        <v>633</v>
-      </c>
       <c r="E249" t="s">
+        <v>619</v>
+      </c>
+      <c r="F249" t="s">
+        <v>615</v>
+      </c>
+      <c r="G249" t="s">
         <v>620</v>
       </c>
-      <c r="F249" t="s">
-        <v>616</v>
-      </c>
-      <c r="G249" t="s">
-        <v>621</v>
-      </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
       </c>
@@ -10850,31 +10850,31 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>633</v>
+      </c>
+      <c r="B250" t="s">
+        <v>611</v>
+      </c>
+      <c r="C250" t="s">
+        <v>612</v>
+      </c>
+      <c r="D250" t="s">
         <v>634</v>
       </c>
-      <c r="B250" t="s">
-        <v>612</v>
-      </c>
-      <c r="C250" t="s">
-        <v>613</v>
-      </c>
-      <c r="D250" t="s">
-        <v>635</v>
-      </c>
       <c r="E250" t="s">
+        <v>614</v>
+      </c>
+      <c r="F250" t="s">
         <v>615</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
         <v>616</v>
       </c>
-      <c r="G250" t="s">
-        <v>617</v>
-      </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
       </c>
@@ -10882,31 +10882,31 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>635</v>
+      </c>
+      <c r="B251" t="s">
+        <v>611</v>
+      </c>
+      <c r="C251" t="s">
+        <v>612</v>
+      </c>
+      <c r="D251" t="s">
         <v>636</v>
       </c>
-      <c r="B251" t="s">
-        <v>612</v>
-      </c>
-      <c r="C251" t="s">
-        <v>613</v>
-      </c>
-      <c r="D251" t="s">
-        <v>637</v>
-      </c>
       <c r="E251" t="s">
+        <v>619</v>
+      </c>
+      <c r="F251" t="s">
+        <v>615</v>
+      </c>
+      <c r="G251" t="s">
         <v>620</v>
       </c>
-      <c r="F251" t="s">
-        <v>616</v>
-      </c>
-      <c r="G251" t="s">
-        <v>621</v>
-      </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
       </c>
@@ -10914,31 +10914,31 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>637</v>
+      </c>
+      <c r="B252" t="s">
+        <v>611</v>
+      </c>
+      <c r="C252" t="s">
+        <v>612</v>
+      </c>
+      <c r="D252" t="s">
         <v>638</v>
       </c>
-      <c r="B252" t="s">
-        <v>612</v>
-      </c>
-      <c r="C252" t="s">
-        <v>613</v>
-      </c>
-      <c r="D252" t="s">
-        <v>639</v>
-      </c>
       <c r="E252" t="s">
+        <v>614</v>
+      </c>
+      <c r="F252" t="s">
         <v>615</v>
       </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
         <v>616</v>
       </c>
-      <c r="G252" t="s">
-        <v>617</v>
-      </c>
       <c r="H252" s="3" t="s">
         <v>53</v>
       </c>
@@ -10946,31 +10946,31 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>639</v>
+      </c>
+      <c r="B253" t="s">
+        <v>611</v>
+      </c>
+      <c r="C253" t="s">
+        <v>612</v>
+      </c>
+      <c r="D253" t="s">
         <v>640</v>
       </c>
-      <c r="B253" t="s">
-        <v>612</v>
-      </c>
-      <c r="C253" t="s">
-        <v>613</v>
-      </c>
-      <c r="D253" t="s">
-        <v>641</v>
-      </c>
       <c r="E253" t="s">
+        <v>619</v>
+      </c>
+      <c r="F253" t="s">
+        <v>615</v>
+      </c>
+      <c r="G253" t="s">
         <v>620</v>
       </c>
-      <c r="F253" t="s">
-        <v>616</v>
-      </c>
-      <c r="G253" t="s">
-        <v>621</v>
-      </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
       </c>
@@ -10978,31 +10978,31 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>641</v>
+      </c>
+      <c r="B254" t="s">
+        <v>611</v>
+      </c>
+      <c r="C254" t="s">
+        <v>612</v>
+      </c>
+      <c r="D254" t="s">
         <v>642</v>
       </c>
-      <c r="B254" t="s">
-        <v>612</v>
-      </c>
-      <c r="C254" t="s">
-        <v>613</v>
-      </c>
-      <c r="D254" t="s">
-        <v>643</v>
-      </c>
       <c r="E254" t="s">
+        <v>614</v>
+      </c>
+      <c r="F254" t="s">
         <v>615</v>
       </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
         <v>616</v>
       </c>
-      <c r="G254" t="s">
-        <v>617</v>
-      </c>
       <c r="H254" s="3" t="s">
         <v>53</v>
       </c>
@@ -11010,31 +11010,31 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>643</v>
+      </c>
+      <c r="B255" t="s">
+        <v>611</v>
+      </c>
+      <c r="C255" t="s">
+        <v>612</v>
+      </c>
+      <c r="D255" t="s">
         <v>644</v>
       </c>
-      <c r="B255" t="s">
-        <v>612</v>
-      </c>
-      <c r="C255" t="s">
-        <v>613</v>
-      </c>
-      <c r="D255" t="s">
-        <v>645</v>
-      </c>
       <c r="E255" t="s">
+        <v>619</v>
+      </c>
+      <c r="F255" t="s">
+        <v>615</v>
+      </c>
+      <c r="G255" t="s">
         <v>620</v>
       </c>
-      <c r="F255" t="s">
-        <v>616</v>
-      </c>
-      <c r="G255" t="s">
-        <v>621</v>
-      </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
       </c>
@@ -11042,31 +11042,31 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>645</v>
+      </c>
+      <c r="B256" t="s">
+        <v>611</v>
+      </c>
+      <c r="C256" t="s">
+        <v>612</v>
+      </c>
+      <c r="D256" t="s">
         <v>646</v>
       </c>
-      <c r="B256" t="s">
-        <v>612</v>
-      </c>
-      <c r="C256" t="s">
-        <v>613</v>
-      </c>
-      <c r="D256" t="s">
-        <v>647</v>
-      </c>
       <c r="E256" t="s">
+        <v>614</v>
+      </c>
+      <c r="F256" t="s">
         <v>615</v>
       </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
         <v>616</v>
       </c>
-      <c r="G256" t="s">
-        <v>617</v>
-      </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
       </c>
@@ -11074,31 +11074,31 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>647</v>
+      </c>
+      <c r="B257" t="s">
+        <v>611</v>
+      </c>
+      <c r="C257" t="s">
+        <v>612</v>
+      </c>
+      <c r="D257" t="s">
         <v>648</v>
       </c>
-      <c r="B257" t="s">
-        <v>612</v>
-      </c>
-      <c r="C257" t="s">
-        <v>613</v>
-      </c>
-      <c r="D257" t="s">
-        <v>649</v>
-      </c>
       <c r="E257" t="s">
+        <v>619</v>
+      </c>
+      <c r="F257" t="s">
+        <v>615</v>
+      </c>
+      <c r="G257" t="s">
         <v>620</v>
       </c>
-      <c r="F257" t="s">
-        <v>616</v>
-      </c>
-      <c r="G257" t="s">
-        <v>621</v>
-      </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
       </c>
@@ -11106,31 +11106,31 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>649</v>
+      </c>
+      <c r="B258" t="s">
+        <v>611</v>
+      </c>
+      <c r="C258" t="s">
+        <v>612</v>
+      </c>
+      <c r="D258" t="s">
         <v>650</v>
       </c>
-      <c r="B258" t="s">
-        <v>612</v>
-      </c>
-      <c r="C258" t="s">
-        <v>613</v>
-      </c>
-      <c r="D258" t="s">
-        <v>651</v>
-      </c>
       <c r="E258" t="s">
+        <v>614</v>
+      </c>
+      <c r="F258" t="s">
         <v>615</v>
       </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
         <v>616</v>
       </c>
-      <c r="G258" t="s">
-        <v>617</v>
-      </c>
       <c r="H258" s="3" t="s">
         <v>53</v>
       </c>
@@ -11138,39 +11138,39 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>651</v>
+      </c>
+      <c r="B259" t="s">
+        <v>611</v>
+      </c>
+      <c r="C259" t="s">
+        <v>612</v>
+      </c>
+      <c r="D259" t="s">
         <v>652</v>
       </c>
-      <c r="B259" t="s">
-        <v>612</v>
-      </c>
-      <c r="C259" t="s">
-        <v>613</v>
-      </c>
-      <c r="D259" t="s">
+      <c r="E259" t="s">
+        <v>619</v>
+      </c>
+      <c r="F259" t="s">
+        <v>615</v>
+      </c>
+      <c r="G259" t="s">
+        <v>620</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I259">
+        <v>1</v>
+      </c>
+      <c r="J259" t="s">
         <v>653</v>
-      </c>
-      <c r="E259" t="s">
-        <v>620</v>
-      </c>
-      <c r="F259" t="s">
-        <v>616</v>
-      </c>
-      <c r="G259" t="s">
-        <v>621</v>
-      </c>
-      <c r="H259" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I259">
-        <v>1</v>
-      </c>
-      <c r="J259" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
@@ -11178,23 +11178,23 @@
         <v>654</v>
       </c>
       <c r="B260" t="s">
+        <v>611</v>
+      </c>
+      <c r="C260" t="s">
         <v>612</v>
-      </c>
-      <c r="C260" t="s">
-        <v>613</v>
       </c>
       <c r="D260" t="s">
         <v>655</v>
       </c>
       <c r="E260" t="s">
+        <v>614</v>
+      </c>
+      <c r="F260" t="s">
         <v>615</v>
       </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
         <v>616</v>
       </c>
-      <c r="G260" t="s">
-        <v>617</v>
-      </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
@@ -11210,23 +11210,23 @@
         <v>656</v>
       </c>
       <c r="B261" t="s">
+        <v>611</v>
+      </c>
+      <c r="C261" t="s">
         <v>612</v>
-      </c>
-      <c r="C261" t="s">
-        <v>613</v>
       </c>
       <c r="D261" t="s">
         <v>657</v>
       </c>
       <c r="E261" t="s">
+        <v>619</v>
+      </c>
+      <c r="F261" t="s">
+        <v>615</v>
+      </c>
+      <c r="G261" t="s">
         <v>620</v>
       </c>
-      <c r="F261" t="s">
-        <v>616</v>
-      </c>
-      <c r="G261" t="s">
-        <v>621</v>
-      </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -11242,23 +11242,23 @@
         <v>658</v>
       </c>
       <c r="B262" t="s">
+        <v>611</v>
+      </c>
+      <c r="C262" t="s">
         <v>612</v>
-      </c>
-      <c r="C262" t="s">
-        <v>613</v>
       </c>
       <c r="D262" t="s">
         <v>659</v>
       </c>
       <c r="E262" t="s">
+        <v>614</v>
+      </c>
+      <c r="F262" t="s">
         <v>615</v>
       </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
         <v>616</v>
       </c>
-      <c r="G262" t="s">
-        <v>617</v>
-      </c>
       <c r="H262" s="3" t="s">
         <v>53</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -11274,23 +11274,23 @@
         <v>660</v>
       </c>
       <c r="B263" t="s">
+        <v>611</v>
+      </c>
+      <c r="C263" t="s">
         <v>612</v>
-      </c>
-      <c r="C263" t="s">
-        <v>613</v>
       </c>
       <c r="D263" t="s">
         <v>661</v>
       </c>
       <c r="E263" t="s">
+        <v>619</v>
+      </c>
+      <c r="F263" t="s">
+        <v>615</v>
+      </c>
+      <c r="G263" t="s">
         <v>620</v>
       </c>
-      <c r="F263" t="s">
-        <v>616</v>
-      </c>
-      <c r="G263" t="s">
-        <v>621</v>
-      </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -11306,23 +11306,23 @@
         <v>662</v>
       </c>
       <c r="B264" t="s">
+        <v>611</v>
+      </c>
+      <c r="C264" t="s">
         <v>612</v>
-      </c>
-      <c r="C264" t="s">
-        <v>613</v>
       </c>
       <c r="D264" t="s">
         <v>663</v>
       </c>
       <c r="E264" t="s">
+        <v>614</v>
+      </c>
+      <c r="F264" t="s">
         <v>615</v>
       </c>
-      <c r="F264" t="s">
+      <c r="G264" t="s">
         <v>616</v>
       </c>
-      <c r="G264" t="s">
-        <v>617</v>
-      </c>
       <c r="H264" s="3" t="s">
         <v>53</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -11338,23 +11338,23 @@
         <v>664</v>
       </c>
       <c r="B265" t="s">
+        <v>611</v>
+      </c>
+      <c r="C265" t="s">
         <v>612</v>
-      </c>
-      <c r="C265" t="s">
-        <v>613</v>
       </c>
       <c r="D265" t="s">
         <v>665</v>
       </c>
       <c r="E265" t="s">
+        <v>619</v>
+      </c>
+      <c r="F265" t="s">
+        <v>615</v>
+      </c>
+      <c r="G265" t="s">
         <v>620</v>
       </c>
-      <c r="F265" t="s">
-        <v>616</v>
-      </c>
-      <c r="G265" t="s">
-        <v>621</v>
-      </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -11370,23 +11370,23 @@
         <v>666</v>
       </c>
       <c r="B266" t="s">
+        <v>611</v>
+      </c>
+      <c r="C266" t="s">
         <v>612</v>
-      </c>
-      <c r="C266" t="s">
-        <v>613</v>
       </c>
       <c r="D266" t="s">
         <v>667</v>
       </c>
       <c r="E266" t="s">
+        <v>614</v>
+      </c>
+      <c r="F266" t="s">
         <v>615</v>
       </c>
-      <c r="F266" t="s">
+      <c r="G266" t="s">
         <v>616</v>
       </c>
-      <c r="G266" t="s">
-        <v>617</v>
-      </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -11402,23 +11402,23 @@
         <v>668</v>
       </c>
       <c r="B267" t="s">
+        <v>611</v>
+      </c>
+      <c r="C267" t="s">
         <v>612</v>
-      </c>
-      <c r="C267" t="s">
-        <v>613</v>
       </c>
       <c r="D267" t="s">
         <v>669</v>
       </c>
       <c r="E267" t="s">
+        <v>619</v>
+      </c>
+      <c r="F267" t="s">
+        <v>615</v>
+      </c>
+      <c r="G267" t="s">
         <v>620</v>
       </c>
-      <c r="F267" t="s">
-        <v>616</v>
-      </c>
-      <c r="G267" t="s">
-        <v>621</v>
-      </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -11434,23 +11434,23 @@
         <v>670</v>
       </c>
       <c r="B268" t="s">
+        <v>611</v>
+      </c>
+      <c r="C268" t="s">
         <v>612</v>
-      </c>
-      <c r="C268" t="s">
-        <v>613</v>
       </c>
       <c r="D268" t="s">
         <v>671</v>
       </c>
       <c r="E268" t="s">
+        <v>614</v>
+      </c>
+      <c r="F268" t="s">
         <v>615</v>
       </c>
-      <c r="F268" t="s">
+      <c r="G268" t="s">
         <v>616</v>
       </c>
-      <c r="G268" t="s">
-        <v>617</v>
-      </c>
       <c r="H268" s="3" t="s">
         <v>53</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -11466,23 +11466,23 @@
         <v>672</v>
       </c>
       <c r="B269" t="s">
+        <v>611</v>
+      </c>
+      <c r="C269" t="s">
         <v>612</v>
-      </c>
-      <c r="C269" t="s">
-        <v>613</v>
       </c>
       <c r="D269" t="s">
         <v>673</v>
       </c>
       <c r="E269" t="s">
+        <v>619</v>
+      </c>
+      <c r="F269" t="s">
+        <v>615</v>
+      </c>
+      <c r="G269" t="s">
         <v>620</v>
       </c>
-      <c r="F269" t="s">
-        <v>616</v>
-      </c>
-      <c r="G269" t="s">
-        <v>621</v>
-      </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -11498,23 +11498,23 @@
         <v>674</v>
       </c>
       <c r="B270" t="s">
+        <v>611</v>
+      </c>
+      <c r="C270" t="s">
         <v>612</v>
-      </c>
-      <c r="C270" t="s">
-        <v>613</v>
       </c>
       <c r="D270" t="s">
         <v>675</v>
       </c>
       <c r="E270" t="s">
+        <v>614</v>
+      </c>
+      <c r="F270" t="s">
         <v>615</v>
       </c>
-      <c r="F270" t="s">
+      <c r="G270" t="s">
         <v>616</v>
       </c>
-      <c r="G270" t="s">
-        <v>617</v>
-      </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -11530,23 +11530,23 @@
         <v>676</v>
       </c>
       <c r="B271" t="s">
+        <v>611</v>
+      </c>
+      <c r="C271" t="s">
         <v>612</v>
-      </c>
-      <c r="C271" t="s">
-        <v>613</v>
       </c>
       <c r="D271" t="s">
         <v>677</v>
       </c>
       <c r="E271" t="s">
+        <v>619</v>
+      </c>
+      <c r="F271" t="s">
+        <v>615</v>
+      </c>
+      <c r="G271" t="s">
         <v>620</v>
       </c>
-      <c r="F271" t="s">
-        <v>616</v>
-      </c>
-      <c r="G271" t="s">
-        <v>621</v>
-      </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -11586,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -11618,7 +11618,7 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -11650,7 +11650,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -11682,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -11714,7 +11714,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -11746,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -11778,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -11810,7 +11810,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -11842,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -11874,7 +11874,7 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -11906,7 +11906,7 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -11938,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -11970,7 +11970,7 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -12002,7 +12002,7 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -12034,7 +12034,7 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -12066,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -12098,7 +12098,7 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -12130,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -12162,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -12194,7 +12194,7 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -12226,7 +12226,7 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -12258,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -12290,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -12322,7 +12322,7 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -12354,7 +12354,7 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -12386,7 +12386,7 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -12418,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -12450,7 +12450,7 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -12482,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -12514,7 +12514,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
